--- a/traducao/tecnicas/Tecnicas.xlsx
+++ b/traducao/tecnicas/Tecnicas.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Leia" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +13,7 @@
     <sheet name="Combinações" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -30,10 +29,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <color rgb="00808080"/>
+      <name val="Calibri"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -45,12 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +79,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -473,9 +476,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -518,9 +518,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -534,9 +531,6 @@
           <t>peça 1 nº 113 em diante (仙 "imortal" virou "Sloth's"); a coluna Obs. marca onde o inglês não bate.</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -582,7 +576,7 @@
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -638,8 +632,11 @@
           <t>Hoverer's</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>do Voo</t>
+        </is>
+      </c>
       <c r="G2" s="3">
         <f>IF(F2="","","Técnica Sólida "&amp;F2)</f>
         <v/>
@@ -664,8 +661,11 @@
           <t>Dancer's</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>da Dança</t>
+        </is>
+      </c>
       <c r="G3" s="3">
         <f>IF(F3="","","Técnica Sólida "&amp;F3)</f>
         <v/>
@@ -690,8 +690,11 @@
           <t>Blower's</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>do Sopro</t>
+        </is>
+      </c>
       <c r="G4" s="3">
         <f>IF(F4="","","Técnica Sólida "&amp;F4)</f>
         <v/>
@@ -716,8 +719,11 @@
           <t>Fallen's</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>da Queda</t>
+        </is>
+      </c>
       <c r="G5" s="3">
         <f>IF(F5="","","Técnica Sólida "&amp;F5)</f>
         <v/>
@@ -742,8 +748,11 @@
           <t>Drifter's</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>da Brisa</t>
+        </is>
+      </c>
       <c r="G6" s="3">
         <f>IF(F6="","","Técnica Sólida "&amp;F6)</f>
         <v/>
@@ -768,8 +777,11 @@
           <t>Cutter's</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>da Degola</t>
+        </is>
+      </c>
       <c r="G7" s="3">
         <f>IF(F7="","","Técnica Sólida "&amp;F7)</f>
         <v/>
@@ -794,8 +806,11 @@
           <t>Taken's</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>da Ruptura</t>
+        </is>
+      </c>
       <c r="G8" s="3">
         <f>IF(F8="","","Técnica Sólida "&amp;F8)</f>
         <v/>
@@ -820,8 +835,11 @@
           <t>Thinker's</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>da Condensação</t>
+        </is>
+      </c>
       <c r="G9" s="3">
         <f>IF(F9="","","Técnica Sólida "&amp;F9)</f>
         <v/>
@@ -846,8 +864,11 @@
           <t>Ravager's</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>da Quebra</t>
+        </is>
+      </c>
       <c r="G10" s="3">
         <f>IF(F10="","","Técnica Sólida "&amp;F10)</f>
         <v/>
@@ -872,8 +893,11 @@
           <t>Holder's</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>do Agarre</t>
+        </is>
+      </c>
       <c r="G11" s="3">
         <f>IF(F11="","","Técnica Sólida "&amp;F11)</f>
         <v/>
@@ -898,8 +922,11 @@
           <t>Slicer's</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>do Rasgo</t>
+        </is>
+      </c>
       <c r="G12" s="3">
         <f>IF(F12="","","Técnica Sólida "&amp;F12)</f>
         <v/>
@@ -924,8 +951,11 @@
           <t>Fixer's</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>da Convergência</t>
+        </is>
+      </c>
       <c r="G13" s="3">
         <f>IF(F13="","","Técnica Sólida "&amp;F13)</f>
         <v/>
@@ -950,8 +980,11 @@
           <t>Returner's</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>do Retorno</t>
+        </is>
+      </c>
       <c r="G14" s="3">
         <f>IF(F14="","","Técnica Sólida "&amp;F14)</f>
         <v/>
@@ -976,8 +1009,11 @@
           <t>Forger's</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>da Forja</t>
+        </is>
+      </c>
       <c r="G15" s="3">
         <f>IF(F15="","","Técnica Sólida "&amp;F15)</f>
         <v/>
@@ -1002,8 +1038,11 @@
           <t>Burner's</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>da Incineração</t>
+        </is>
+      </c>
       <c r="G16" s="3">
         <f>IF(F16="","","Técnica Sólida "&amp;F16)</f>
         <v/>
@@ -1028,8 +1067,11 @@
           <t>Befallen's</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>do Colapso</t>
+        </is>
+      </c>
       <c r="G17" s="3">
         <f>IF(F17="","","Técnica Sólida "&amp;F17)</f>
         <v/>
@@ -1054,8 +1096,11 @@
           <t>Seer's</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>da Brasa</t>
+        </is>
+      </c>
       <c r="G18" s="3">
         <f>IF(F18="","","Técnica Sólida "&amp;F18)</f>
         <v/>
@@ -1080,8 +1125,11 @@
           <t>Quietude's</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>da Estase</t>
+        </is>
+      </c>
       <c r="G19" s="3">
         <f>IF(F19="","","Técnica Sólida "&amp;F19)</f>
         <v/>
@@ -1106,8 +1154,11 @@
           <t>Warrior's</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>da Perfuração</t>
+        </is>
+      </c>
       <c r="G20" s="3">
         <f>IF(F20="","","Técnica Sólida "&amp;F20)</f>
         <v/>
@@ -1132,8 +1183,11 @@
           <t>Seal's</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>do Selo</t>
+        </is>
+      </c>
       <c r="G21" s="3">
         <f>IF(F21="","","Técnica Sólida "&amp;F21)</f>
         <v/>
@@ -1158,8 +1212,11 @@
           <t>Moon's</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" s="2" t="n"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>da Lua</t>
+        </is>
+      </c>
       <c r="G22" s="3">
         <f>IF(F22="","","Técnica Sólida "&amp;F22)</f>
         <v/>
@@ -1184,8 +1241,11 @@
           <t>Dragon's</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>do Dragão</t>
+        </is>
+      </c>
       <c r="G23" s="3">
         <f>IF(F23="","","Técnica Sólida "&amp;F23)</f>
         <v/>
@@ -1210,8 +1270,11 @@
           <t>Star's</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>da Estrela</t>
+        </is>
+      </c>
       <c r="G24" s="3">
         <f>IF(F24="","","Técnica Sólida "&amp;F24)</f>
         <v/>
@@ -1236,8 +1299,11 @@
           <t>Cloud's</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>da Nuvem</t>
+        </is>
+      </c>
       <c r="G25" s="3">
         <f>IF(F25="","","Técnica Sólida "&amp;F25)</f>
         <v/>
@@ -1262,8 +1328,11 @@
           <t>Blood's</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>do Sangue</t>
+        </is>
+      </c>
       <c r="G26" s="3">
         <f>IF(F26="","","Técnica Sólida "&amp;F26)</f>
         <v/>
@@ -1288,8 +1357,11 @@
           <t>Spirit's</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>do Divino</t>
+        </is>
+      </c>
       <c r="G27" s="3">
         <f>IF(F27="","","Técnica Sólida "&amp;F27)</f>
         <v/>
@@ -1314,8 +1386,11 @@
           <t>Demon's</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>do Abismo</t>
+        </is>
+      </c>
       <c r="G28" s="3">
         <f>IF(F28="","","Técnica Sólida "&amp;F28)</f>
         <v/>
@@ -1340,8 +1415,11 @@
           <t>Azure's</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>do Firmamento</t>
+        </is>
+      </c>
       <c r="G29" s="3">
         <f>IF(F29="","","Técnica Sólida "&amp;F29)</f>
         <v/>
@@ -1366,8 +1444,11 @@
           <t>Nether's</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>do Purgatório</t>
+        </is>
+      </c>
       <c r="G30" s="3">
         <f>IF(F30="","","Técnica Sólida "&amp;F30)</f>
         <v/>
@@ -1392,8 +1473,11 @@
           <t>Brute's</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" s="2" t="n"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>da Tempestade</t>
+        </is>
+      </c>
       <c r="G31" s="3">
         <f>IF(F31="","","Técnica Sólida "&amp;F31)</f>
         <v/>
@@ -1418,8 +1502,11 @@
           <t>Madness'</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" s="2" t="n"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>da Fúria</t>
+        </is>
+      </c>
       <c r="G32" s="3">
         <f>IF(F32="","","Técnica Sólida "&amp;F32)</f>
         <v/>
@@ -1444,8 +1531,11 @@
           <t>Control's</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" s="2" t="n"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>do Relâmpago</t>
+        </is>
+      </c>
       <c r="G33" s="3">
         <f>IF(F33="","","Técnica Sólida "&amp;F33)</f>
         <v/>
@@ -1470,8 +1560,11 @@
           <t>Hunger's</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" s="2" t="n"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>da Devoração</t>
+        </is>
+      </c>
       <c r="G34" s="3">
         <f>IF(F34="","","Técnica Sólida "&amp;F34)</f>
         <v/>
@@ -1496,8 +1589,11 @@
           <t>Turn's</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" s="2" t="n"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>da Transmutação</t>
+        </is>
+      </c>
       <c r="G35" s="3">
         <f>IF(F35="","","Técnica Sólida "&amp;F35)</f>
         <v/>
@@ -1522,8 +1618,11 @@
           <t>Death's</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" s="2" t="n"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>do Regicídio</t>
+        </is>
+      </c>
       <c r="G36" s="3">
         <f>IF(F36="","","Técnica Sólida "&amp;F36)</f>
         <v/>
@@ -1548,8 +1647,11 @@
           <t>Void's</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" s="2" t="n"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>do Nada</t>
+        </is>
+      </c>
       <c r="G37" s="3">
         <f>IF(F37="","","Técnica Sólida "&amp;F37)</f>
         <v/>
@@ -1574,8 +1676,11 @@
           <t>Outcast's</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" s="2" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>do Ermitão</t>
+        </is>
+      </c>
       <c r="G38" s="3">
         <f>IF(F38="","","Técnica Sólida "&amp;F38)</f>
         <v/>
@@ -1600,8 +1705,11 @@
           <t>Wanderer's</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" s="2" t="n"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>do Fluxo</t>
+        </is>
+      </c>
       <c r="G39" s="3">
         <f>IF(F39="","","Técnica Sólida "&amp;F39)</f>
         <v/>
@@ -1626,8 +1734,11 @@
           <t>Trap's</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" s="2" t="n"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>da Emboscada</t>
+        </is>
+      </c>
       <c r="G40" s="3">
         <f>IF(F40="","","Técnica Sólida "&amp;F40)</f>
         <v/>
@@ -1652,8 +1763,11 @@
           <t>Wreckage's</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" s="2" t="n"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>do Esmagamento</t>
+        </is>
+      </c>
       <c r="G41" s="3">
         <f>IF(F41="","","Técnica Sólida "&amp;F41)</f>
         <v/>
@@ -1678,8 +1792,11 @@
           <t>City's</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" s="2" t="n"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>da Subjugação</t>
+        </is>
+      </c>
       <c r="G42" s="3">
         <f>IF(F42="","","Técnica Sólida "&amp;F42)</f>
         <v/>
@@ -1704,8 +1821,11 @@
           <t>Canal's</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" s="2" t="n"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>da Travessia</t>
+        </is>
+      </c>
       <c r="G43" s="3">
         <f>IF(F43="","","Técnica Sólida "&amp;F43)</f>
         <v/>
@@ -1730,8 +1850,11 @@
           <t>Thief's</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" s="2" t="n"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>da Usurpação</t>
+        </is>
+      </c>
       <c r="G44" s="3">
         <f>IF(F44="","","Técnica Sólida "&amp;F44)</f>
         <v/>
@@ -1756,8 +1879,11 @@
           <t>Crusher's</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" s="2" t="n"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>da Fragmentação</t>
+        </is>
+      </c>
       <c r="G45" s="3">
         <f>IF(F45="","","Técnica Sólida "&amp;F45)</f>
         <v/>
@@ -1782,8 +1908,11 @@
           <t>Ruiner's</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" s="2" t="n"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>da Aniquilação</t>
+        </is>
+      </c>
       <c r="G46" s="3">
         <f>IF(F46="","","Técnica Sólida "&amp;F46)</f>
         <v/>
@@ -1808,8 +1937,11 @@
           <t>Feather's</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" s="2" t="n"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>da Leveza</t>
+        </is>
+      </c>
       <c r="G47" s="3">
         <f>IF(F47="","","Técnica Sólida "&amp;F47)</f>
         <v/>
@@ -1834,8 +1966,11 @@
           <t>Ender's</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" s="2" t="n"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>do Ultimato</t>
+        </is>
+      </c>
       <c r="G48" s="3">
         <f>IF(F48="","","Técnica Sólida "&amp;F48)</f>
         <v/>
@@ -1860,8 +1995,11 @@
           <t>Gloom's</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" s="2" t="n"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>do Recôndito</t>
+        </is>
+      </c>
       <c r="G49" s="3">
         <f>IF(F49="","","Técnica Sólida "&amp;F49)</f>
         <v/>
@@ -1886,8 +2024,11 @@
           <t>Cobalt's</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" s="2" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>do Jade</t>
+        </is>
+      </c>
       <c r="G50" s="3">
         <f>IF(F50="","","Técnica Sólida "&amp;F50)</f>
         <v/>
@@ -1912,8 +2053,11 @@
           <t>Gore's</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" s="2" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>do Carmesim</t>
+        </is>
+      </c>
       <c r="G51" s="3">
         <f>IF(F51="","","Técnica Sólida "&amp;F51)</f>
         <v/>
@@ -1938,8 +2082,11 @@
           <t>Gilder's</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" s="2" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>do Ouro</t>
+        </is>
+      </c>
       <c r="G52" s="3">
         <f>IF(F52="","","Técnica Sólida "&amp;F52)</f>
         <v/>
@@ -1964,8 +2111,11 @@
           <t>Obsidian's</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" s="2" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>do Ébano</t>
+        </is>
+      </c>
       <c r="G53" s="3">
         <f>IF(F53="","","Técnica Sólida "&amp;F53)</f>
         <v/>
@@ -1990,8 +2140,11 @@
           <t>Ruby's</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" s="2" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>do Escarlate</t>
+        </is>
+      </c>
       <c r="G54" s="3">
         <f>IF(F54="","","Técnica Sólida "&amp;F54)</f>
         <v/>
@@ -2016,8 +2169,11 @@
           <t>Silver's</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" s="2" t="n"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>da Prata</t>
+        </is>
+      </c>
       <c r="G55" s="3">
         <f>IF(F55="","","Técnica Sólida "&amp;F55)</f>
         <v/>
@@ -2042,8 +2198,11 @@
           <t>Sealer's</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" s="2" t="n"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>do Tabu</t>
+        </is>
+      </c>
       <c r="G56" s="3">
         <f>IF(F56="","","Técnica Sólida "&amp;F56)</f>
         <v/>
@@ -2068,8 +2227,11 @@
           <t>Goner's</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" s="2" t="n"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>da Mutilação</t>
+        </is>
+      </c>
       <c r="G57" s="3">
         <f>IF(F57="","","Técnica Sólida "&amp;F57)</f>
         <v/>
@@ -2094,8 +2256,11 @@
           <t>Sky's</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" s="2" t="n"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>do Céu</t>
+        </is>
+      </c>
       <c r="G58" s="3">
         <f>IF(F58="","","Técnica Sólida "&amp;F58)</f>
         <v/>
@@ -2120,8 +2285,11 @@
           <t>Mirage's</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" s="2" t="n"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>da Ilusão</t>
+        </is>
+      </c>
       <c r="G59" s="3">
         <f>IF(F59="","","Técnica Sólida "&amp;F59)</f>
         <v/>
@@ -2146,8 +2314,11 @@
           <t>Alacrity's</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" s="2" t="n"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>da Velocidade</t>
+        </is>
+      </c>
       <c r="G60" s="3">
         <f>IF(F60="","","Técnica Sólida "&amp;F60)</f>
         <v/>
@@ -2172,8 +2343,11 @@
           <t>Anger's</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" s="2" t="n"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>da Ira</t>
+        </is>
+      </c>
       <c r="G61" s="3">
         <f>IF(F61="","","Técnica Sólida "&amp;F61)</f>
         <v/>
@@ -2198,8 +2372,11 @@
           <t>Flare's</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="2" t="n"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>da Incandescência</t>
+        </is>
+      </c>
       <c r="G62" s="3">
         <f>IF(F62="","","Técnica Sólida "&amp;F62)</f>
         <v/>
@@ -2224,8 +2401,11 @@
           <t>Aether's</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" s="2" t="n"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>do Éter</t>
+        </is>
+      </c>
       <c r="G63" s="3">
         <f>IF(F63="","","Técnica Sólida "&amp;F63)</f>
         <v/>
@@ -2250,8 +2430,11 @@
           <t>Inker's</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" s="2" t="n"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>do Nanquim</t>
+        </is>
+      </c>
       <c r="G64" s="3">
         <f>IF(F64="","","Técnica Sólida "&amp;F64)</f>
         <v/>
@@ -2276,8 +2459,11 @@
           <t>Chainer's</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" s="2" t="n"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>das Correntes</t>
+        </is>
+      </c>
       <c r="G65" s="3">
         <f>IF(F65="","","Técnica Sólida "&amp;F65)</f>
         <v/>
@@ -2302,8 +2488,11 @@
           <t>Wielder's</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" s="2" t="n"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>do Domínio</t>
+        </is>
+      </c>
       <c r="G66" s="3">
         <f>IF(F66="","","Técnica Sólida "&amp;F66)</f>
         <v/>
@@ -2328,8 +2517,11 @@
           <t>Deserter's</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" s="2" t="n"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>do Vácuo</t>
+        </is>
+      </c>
       <c r="G67" s="3">
         <f>IF(F67="","","Técnica Sólida "&amp;F67)</f>
         <v/>
@@ -2354,8 +2546,11 @@
           <t>Doom's</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" s="2" t="n"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>da Escuridão</t>
+        </is>
+      </c>
       <c r="G68" s="3">
         <f>IF(F68="","","Técnica Sólida "&amp;F68)</f>
         <v/>
@@ -2380,8 +2575,11 @@
           <t>Evil's</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" s="2" t="n"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>do Maligno</t>
+        </is>
+      </c>
       <c r="G69" s="3">
         <f>IF(F69="","","Técnica Sólida "&amp;F69)</f>
         <v/>
@@ -2406,8 +2604,11 @@
           <t>Waste's</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>do Ermo</t>
+        </is>
+      </c>
       <c r="G70" s="3">
         <f>IF(F70="","","Técnica Sólida "&amp;F70)</f>
         <v/>
@@ -2432,8 +2633,11 @@
           <t>Gnawer's</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>da Corrosão</t>
+        </is>
+      </c>
       <c r="G71" s="3">
         <f>IF(F71="","","Técnica Sólida "&amp;F71)</f>
         <v/>
@@ -2458,8 +2662,11 @@
           <t>Silence's</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" s="2" t="n"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>do Silêncio</t>
+        </is>
+      </c>
       <c r="G72" s="3">
         <f>IF(F72="","","Técnica Sólida "&amp;F72)</f>
         <v/>
@@ -2484,8 +2691,11 @@
           <t>Burster's</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" s="2" t="n"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>da Explosão</t>
+        </is>
+      </c>
       <c r="G73" s="3">
         <f>IF(F73="","","Técnica Sólida "&amp;F73)</f>
         <v/>
@@ -2510,8 +2720,11 @@
           <t>Tearer's</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" s="2" t="n"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>da Fenda</t>
+        </is>
+      </c>
       <c r="G74" s="3">
         <f>IF(F74="","","Técnica Sólida "&amp;F74)</f>
         <v/>
@@ -2536,8 +2749,11 @@
           <t>Suffering's</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" s="2" t="n"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>da Calamidade</t>
+        </is>
+      </c>
       <c r="G75" s="3">
         <f>IF(F75="","","Técnica Sólida "&amp;F75)</f>
         <v/>
@@ -2562,8 +2778,11 @@
           <t>Piercer's</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" s="2" t="n"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>do Trespasso</t>
+        </is>
+      </c>
       <c r="G76" s="3">
         <f>IF(F76="","","Técnica Sólida "&amp;F76)</f>
         <v/>
@@ -2588,8 +2807,11 @@
           <t>Tremor's</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" s="2" t="n"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>do Tremor</t>
+        </is>
+      </c>
       <c r="G77" s="3">
         <f>IF(F77="","","Técnica Sólida "&amp;F77)</f>
         <v/>
@@ -2614,8 +2836,11 @@
           <t>Mystic's</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" s="2" t="n"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>do Profundo</t>
+        </is>
+      </c>
       <c r="G78" s="3">
         <f>IF(F78="","","Técnica Sólida "&amp;F78)</f>
         <v/>
@@ -2640,8 +2865,11 @@
           <t>Jade's</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" s="2" t="n"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>da Esmeralda</t>
+        </is>
+      </c>
       <c r="G79" s="3">
         <f>IF(F79="","","Técnica Sólida "&amp;F79)</f>
         <v/>
@@ -2666,8 +2894,11 @@
           <t>Violet's</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" s="2" t="n"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>da Púrpura</t>
+        </is>
+      </c>
       <c r="G80" s="3">
         <f>IF(F80="","","Técnica Sólida "&amp;F80)</f>
         <v/>
@@ -2692,8 +2923,11 @@
           <t>Miasma's</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" s="2" t="n"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>do Agouro</t>
+        </is>
+      </c>
       <c r="G81" s="3">
         <f>IF(F81="","","Técnica Sólida "&amp;F81)</f>
         <v/>
@@ -2718,8 +2952,11 @@
           <t>Expeller's</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" s="2" t="n"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>do Exílio</t>
+        </is>
+      </c>
       <c r="G82" s="3">
         <f>IF(F82="","","Técnica Sólida "&amp;F82)</f>
         <v/>
@@ -2744,8 +2981,11 @@
           <t>King's</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" s="2" t="n"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>do Zênite</t>
+        </is>
+      </c>
       <c r="G83" s="3">
         <f>IF(F83="","","Técnica Sólida "&amp;F83)</f>
         <v/>
@@ -2770,8 +3010,11 @@
           <t>Seeker's</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" s="2" t="n"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>do Mar Vasto</t>
+        </is>
+      </c>
       <c r="G84" s="3">
         <f>IF(F84="","","Técnica Sólida "&amp;F84)</f>
         <v/>
@@ -2796,8 +3039,11 @@
           <t>Origin's</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" s="2" t="n"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>da Origem</t>
+        </is>
+      </c>
       <c r="G85" s="3">
         <f>IF(F85="","","Técnica Sólida "&amp;F85)</f>
         <v/>
@@ -2822,8 +3068,11 @@
           <t>Melter's</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" s="2" t="n"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>da Fusão</t>
+        </is>
+      </c>
       <c r="G86" s="3">
         <f>IF(F86="","","Técnica Sólida "&amp;F86)</f>
         <v/>
@@ -2848,8 +3097,11 @@
           <t>Boomer's</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" s="2" t="n"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>do Estrondo</t>
+        </is>
+      </c>
       <c r="G87" s="3">
         <f>IF(F87="","","Técnica Sólida "&amp;F87)</f>
         <v/>
@@ -2874,8 +3126,11 @@
           <t>Loner's</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" s="2" t="n"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>do Solitário</t>
+        </is>
+      </c>
       <c r="G88" s="3">
         <f>IF(F88="","","Técnica Sólida "&amp;F88)</f>
         <v/>
@@ -2900,8 +3155,11 @@
           <t>Refraction's</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" s="2" t="n"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>da Dobra</t>
+        </is>
+      </c>
       <c r="G89" s="3">
         <f>IF(F89="","","Técnica Sólida "&amp;F89)</f>
         <v/>
@@ -2926,8 +3184,11 @@
           <t>Sun's</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" s="2" t="n"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>do Yang</t>
+        </is>
+      </c>
       <c r="G90" s="3">
         <f>IF(F90="","","Técnica Sólida "&amp;F90)</f>
         <v/>
@@ -2952,8 +3213,11 @@
           <t>Rain's</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" s="2" t="n"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>da Chuva</t>
+        </is>
+      </c>
       <c r="G91" s="3">
         <f>IF(F91="","","Técnica Sólida "&amp;F91)</f>
         <v/>
@@ -2978,8 +3242,11 @@
           <t>Chaser's</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" s="2" t="n"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>da Perseguição</t>
+        </is>
+      </c>
       <c r="G92" s="3">
         <f>IF(F92="","","Técnica Sólida "&amp;F92)</f>
         <v/>
@@ -3004,8 +3271,11 @@
           <t>Washer's</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" s="2" t="n"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>da Alvura</t>
+        </is>
+      </c>
       <c r="G93" s="3">
         <f>IF(F93="","","Técnica Sólida "&amp;F93)</f>
         <v/>
@@ -3030,8 +3300,11 @@
           <t>Night's</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" s="2" t="n"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>da Noite</t>
+        </is>
+      </c>
       <c r="G94" s="3">
         <f>IF(F94="","","Técnica Sólida "&amp;F94)</f>
         <v/>
@@ -3056,8 +3329,11 @@
           <t>Devourer's</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" s="2" t="n"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>da Fome</t>
+        </is>
+      </c>
       <c r="G95" s="3">
         <f>IF(F95="","","Técnica Sólida "&amp;F95)</f>
         <v/>
@@ -3082,8 +3358,11 @@
           <t>Haste's</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" s="2" t="n"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>da Rapidez</t>
+        </is>
+      </c>
       <c r="G96" s="3">
         <f>IF(F96="","","Técnica Sólida "&amp;F96)</f>
         <v/>
@@ -3108,8 +3387,11 @@
           <t>Hell's</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" s="2" t="n"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>do Mar Escuro</t>
+        </is>
+      </c>
       <c r="G97" s="3">
         <f>IF(F97="","","Técnica Sólida "&amp;F97)</f>
         <v/>
@@ -3134,8 +3416,11 @@
           <t>Razor's</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" s="2" t="n"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>da Geada</t>
+        </is>
+      </c>
       <c r="G98" s="3">
         <f>IF(F98="","","Técnica Sólida "&amp;F98)</f>
         <v/>
@@ -3160,8 +3445,11 @@
           <t>Blaze's</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" s="2" t="n"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>do Incêndio</t>
+        </is>
+      </c>
       <c r="G99" s="3">
         <f>IF(F99="","","Técnica Sólida "&amp;F99)</f>
         <v/>
@@ -3186,8 +3474,11 @@
           <t>Shadow's</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" s="2" t="n"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>da Sombra</t>
+        </is>
+      </c>
       <c r="G100" s="3">
         <f>IF(F100="","","Técnica Sólida "&amp;F100)</f>
         <v/>
@@ -3212,8 +3503,11 @@
           <t>Emperor's</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" s="2" t="n"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>da Supremacia</t>
+        </is>
+      </c>
       <c r="G101" s="3">
         <f>IF(F101="","","Técnica Sólida "&amp;F101)</f>
         <v/>
@@ -3238,8 +3532,11 @@
           <t>Edge's</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" s="2" t="n"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>da Imponência</t>
+        </is>
+      </c>
       <c r="G102" s="3">
         <f>IF(F102="","","Técnica Sólida "&amp;F102)</f>
         <v/>
@@ -3264,8 +3561,11 @@
           <t>Killer's</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" s="2" t="n"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>do Lampejo</t>
+        </is>
+      </c>
       <c r="G103" s="3">
         <f>IF(F103="","","Técnica Sólida "&amp;F103)</f>
         <v/>
@@ -3290,8 +3590,11 @@
           <t>Blessed's</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" s="2" t="n"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>da Pureza</t>
+        </is>
+      </c>
       <c r="G104" s="3">
         <f>IF(F104="","","Técnica Sólida "&amp;F104)</f>
         <v/>
@@ -3316,8 +3619,11 @@
           <t>Roar's</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" s="2" t="n"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>do Uivo</t>
+        </is>
+      </c>
       <c r="G105" s="3">
         <f>IF(F105="","","Técnica Sólida "&amp;F105)</f>
         <v/>
@@ -3342,8 +3648,11 @@
           <t>Rider's</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" s="2" t="n"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>do Galope</t>
+        </is>
+      </c>
       <c r="G106" s="3">
         <f>IF(F106="","","Técnica Sólida "&amp;F106)</f>
         <v/>
@@ -3368,8 +3677,11 @@
           <t>Fear's</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" s="2" t="n"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>do Espanto</t>
+        </is>
+      </c>
       <c r="G107" s="3">
         <f>IF(F107="","","Técnica Sólida "&amp;F107)</f>
         <v/>
@@ -3394,8 +3706,11 @@
           <t>Piner's</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" s="2" t="n"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>do Pensamento</t>
+        </is>
+      </c>
       <c r="G108" s="3">
         <f>IF(F108="","","Técnica Sólida "&amp;F108)</f>
         <v/>
@@ -3420,8 +3735,11 @@
           <t>Blocker's</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" s="2" t="n"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>do Eclipse</t>
+        </is>
+      </c>
       <c r="G109" s="3">
         <f>IF(F109="","","Técnica Sólida "&amp;F109)</f>
         <v/>
@@ -3446,8 +3764,11 @@
           <t>Foreigner's</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" s="2" t="n"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>do Horizonte</t>
+        </is>
+      </c>
       <c r="G110" s="3">
         <f>IF(F110="","","Técnica Sólida "&amp;F110)</f>
         <v/>
@@ -3472,8 +3793,11 @@
           <t>Dead's</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" s="2" t="n"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>do Meteoro</t>
+        </is>
+      </c>
       <c r="G111" s="3">
         <f>IF(F111="","","Técnica Sólida "&amp;F111)</f>
         <v/>
@@ -3498,8 +3822,11 @@
           <t>Rusher's</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" s="2" t="n"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>da Arremetida</t>
+        </is>
+      </c>
       <c r="G112" s="3">
         <f>IF(F112="","","Técnica Sólida "&amp;F112)</f>
         <v/>
@@ -3524,8 +3851,11 @@
           <t>Runner's</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" s="2" t="n"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>da Corrida</t>
+        </is>
+      </c>
       <c r="G113" s="3">
         <f>IF(F113="","","Técnica Sólida "&amp;F113)</f>
         <v/>
@@ -3555,7 +3885,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F114" s="2" t="n"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>da Ferocidade</t>
+        </is>
+      </c>
       <c r="G114" s="3">
         <f>IF(F114="","","Técnica Sólida "&amp;F114)</f>
         <v/>
@@ -3585,7 +3919,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F115" s="2" t="n"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>da Metade</t>
+        </is>
+      </c>
       <c r="G115" s="3">
         <f>IF(F115="","","Técnica Sólida "&amp;F115)</f>
         <v/>
@@ -3615,7 +3953,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F116" s="2" t="n"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>do Peso</t>
+        </is>
+      </c>
       <c r="G116" s="3">
         <f>IF(F116="","","Técnica Sólida "&amp;F116)</f>
         <v/>
@@ -3645,7 +3987,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F117" s="2" t="n"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>do Supremo</t>
+        </is>
+      </c>
       <c r="G117" s="3">
         <f>IF(F117="","","Técnica Sólida "&amp;F117)</f>
         <v/>
@@ -3675,7 +4021,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F118" s="2" t="n"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>da Imensidão</t>
+        </is>
+      </c>
       <c r="G118" s="3">
         <f>IF(F118="","","Técnica Sólida "&amp;F118)</f>
         <v/>
@@ -3705,7 +4055,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F119" s="2" t="n"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>do Transbordo</t>
+        </is>
+      </c>
       <c r="G119" s="3">
         <f>IF(F119="","","Técnica Sólida "&amp;F119)</f>
         <v/>
@@ -3735,7 +4089,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F120" s="2" t="n"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>da Execução</t>
+        </is>
+      </c>
       <c r="G120" s="3">
         <f>IF(F120="","","Técnica Sólida "&amp;F120)</f>
         <v/>
@@ -3765,7 +4123,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F121" s="2" t="n"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>do Inverso</t>
+        </is>
+      </c>
       <c r="G121" s="3">
         <f>IF(F121="","","Técnica Sólida "&amp;F121)</f>
         <v/>
@@ -3795,7 +4157,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F122" s="2" t="n"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>do Fendimento</t>
+        </is>
+      </c>
       <c r="G122" s="3">
         <f>IF(F122="","","Técnica Sólida "&amp;F122)</f>
         <v/>
@@ -3825,7 +4191,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F123" s="2" t="n"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>do Turbilhão</t>
+        </is>
+      </c>
       <c r="G123" s="3">
         <f>IF(F123="","","Técnica Sólida "&amp;F123)</f>
         <v/>
@@ -3855,7 +4225,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F124" s="2" t="n"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>da Tormenta</t>
+        </is>
+      </c>
       <c r="G124" s="3">
         <f>IF(F124="","","Técnica Sólida "&amp;F124)</f>
         <v/>
@@ -3885,7 +4259,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F125" s="2" t="n"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>do Desenfreado</t>
+        </is>
+      </c>
       <c r="G125" s="3">
         <f>IF(F125="","","Técnica Sólida "&amp;F125)</f>
         <v/>
@@ -3915,7 +4293,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F126" s="2" t="n"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>da Suavidade</t>
+        </is>
+      </c>
       <c r="G126" s="3">
         <f>IF(F126="","","Técnica Sólida "&amp;F126)</f>
         <v/>
@@ -3945,7 +4327,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F127" s="2" t="n"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>do Zen</t>
+        </is>
+      </c>
       <c r="G127" s="3">
         <f>IF(F127="","","Técnica Sólida "&amp;F127)</f>
         <v/>
@@ -3975,7 +4361,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F128" s="2" t="n"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>do Imortal</t>
+        </is>
+      </c>
       <c r="G128" s="3">
         <f>IF(F128="","","Técnica Sólida "&amp;F128)</f>
         <v/>
@@ -4005,7 +4395,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F129" s="2" t="n"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>do Braseiro</t>
+        </is>
+      </c>
       <c r="G129" s="3">
         <f>IF(F129="","","Técnica Sólida "&amp;F129)</f>
         <v/>
@@ -4035,7 +4429,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F130" s="2" t="n"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>do Inferno</t>
+        </is>
+      </c>
       <c r="G130" s="3">
         <f>IF(F130="","","Técnica Sólida "&amp;F130)</f>
         <v/>
@@ -4065,7 +4463,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F131" s="2" t="n"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>do Desastre</t>
+        </is>
+      </c>
       <c r="G131" s="3">
         <f>IF(F131="","","Técnica Sólida "&amp;F131)</f>
         <v/>
@@ -4095,7 +4497,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F132" s="2" t="n"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>do Yin</t>
+        </is>
+      </c>
       <c r="G132" s="3">
         <f>IF(F132="","","Técnica Sólida "&amp;F132)</f>
         <v/>
@@ -4125,7 +4531,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F133" s="2" t="n"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>da Lua Nova</t>
+        </is>
+      </c>
       <c r="G133" s="3">
         <f>IF(F133="","","Técnica Sólida "&amp;F133)</f>
         <v/>
@@ -4155,7 +4565,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F134" s="2" t="n"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>da Ursa Maior</t>
+        </is>
+      </c>
       <c r="G134" s="3">
         <f>IF(F134="","","Técnica Sólida "&amp;F134)</f>
         <v/>
@@ -4185,7 +4599,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F135" s="2" t="n"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>da Podridão</t>
+        </is>
+      </c>
       <c r="G135" s="3">
         <f>IF(F135="","","Técnica Sólida "&amp;F135)</f>
         <v/>
@@ -4215,7 +4633,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F136" s="2" t="n"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>do Tigre</t>
+        </is>
+      </c>
       <c r="G136" s="3">
         <f>IF(F136="","","Técnica Sólida "&amp;F136)</f>
         <v/>
@@ -4245,7 +4667,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F137" s="2" t="n"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>da Vontade</t>
+        </is>
+      </c>
       <c r="G137" s="3">
         <f>IF(F137="","","Técnica Sólida "&amp;F137)</f>
         <v/>
@@ -4275,7 +4701,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F138" s="2" t="n"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>da Bigorna</t>
+        </is>
+      </c>
       <c r="G138" s="3">
         <f>IF(F138="","","Técnica Sólida "&amp;F138)</f>
         <v/>
@@ -4305,7 +4735,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F139" s="2" t="n"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>da Libertação</t>
+        </is>
+      </c>
       <c r="G139" s="3">
         <f>IF(F139="","","Técnica Sólida "&amp;F139)</f>
         <v/>
@@ -4335,7 +4769,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F140" s="2" t="n"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>do Sorvo</t>
+        </is>
+      </c>
       <c r="G140" s="3">
         <f>IF(F140="","","Técnica Sólida "&amp;F140)</f>
         <v/>
@@ -4365,7 +4803,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F141" s="2" t="n"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>do Vício</t>
+        </is>
+      </c>
       <c r="G141" s="3">
         <f>IF(F141="","","Técnica Sólida "&amp;F141)</f>
         <v/>
@@ -4395,7 +4837,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F142" s="2" t="n"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>do Giro</t>
+        </is>
+      </c>
       <c r="G142" s="3">
         <f>IF(F142="","","Técnica Sólida "&amp;F142)</f>
         <v/>
@@ -4425,7 +4871,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F143" s="2" t="n"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>da Esquiva</t>
+        </is>
+      </c>
       <c r="G143" s="3">
         <f>IF(F143="","","Técnica Sólida "&amp;F143)</f>
         <v/>
@@ -4455,7 +4905,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F144" s="2" t="n"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>do Instante</t>
+        </is>
+      </c>
       <c r="G144" s="3">
         <f>IF(F144="","","Técnica Sólida "&amp;F144)</f>
         <v/>
@@ -4485,7 +4939,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F145" s="2" t="n"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>do Ódio</t>
+        </is>
+      </c>
       <c r="G145" s="3">
         <f>IF(F145="","","Técnica Sólida "&amp;F145)</f>
         <v/>
@@ -4515,7 +4973,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F146" s="2" t="n"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>do Gigante</t>
+        </is>
+      </c>
       <c r="G146" s="3">
         <f>IF(F146="","","Técnica Sólida "&amp;F146)</f>
         <v/>
@@ -4545,7 +5007,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F147" s="2" t="n"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>do Manto</t>
+        </is>
+      </c>
       <c r="G147" s="3">
         <f>IF(F147="","","Técnica Sólida "&amp;F147)</f>
         <v/>
@@ -4575,7 +5041,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F148" s="2" t="n"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>do Fantasma</t>
+        </is>
+      </c>
       <c r="G148" s="3">
         <f>IF(F148="","","Técnica Sólida "&amp;F148)</f>
         <v/>
@@ -4605,7 +5075,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F149" s="2" t="n"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>da Subjugação</t>
+        </is>
+      </c>
       <c r="G149" s="3">
         <f>IF(F149="","","Técnica Sólida "&amp;F149)</f>
         <v/>
@@ -4635,7 +5109,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F150" s="2" t="n"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>dos Seis</t>
+        </is>
+      </c>
       <c r="G150" s="3">
         <f>IF(F150="","","Técnica Sólida "&amp;F150)</f>
         <v/>
@@ -4665,7 +5143,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F151" s="2" t="n"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>do Espelho</t>
+        </is>
+      </c>
       <c r="G151" s="3">
         <f>IF(F151="","","Técnica Sólida "&amp;F151)</f>
         <v/>
@@ -4695,7 +5177,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F152" s="2" t="n"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>do Prisioneiro</t>
+        </is>
+      </c>
       <c r="G152" s="3">
         <f>IF(F152="","","Técnica Sólida "&amp;F152)</f>
         <v/>
@@ -4725,7 +5211,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F153" s="2" t="n"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>da União</t>
+        </is>
+      </c>
       <c r="G153" s="3">
         <f>IF(F153="","","Técnica Sólida "&amp;F153)</f>
         <v/>
@@ -4755,7 +5245,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F154" s="2" t="n"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>do Brilho</t>
+        </is>
+      </c>
       <c r="G154" s="3">
         <f>IF(F154="","","Técnica Sólida "&amp;F154)</f>
         <v/>
@@ -4785,7 +5279,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F155" s="2" t="n"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>da Seda</t>
+        </is>
+      </c>
       <c r="G155" s="3">
         <f>IF(F155="","","Técnica Sólida "&amp;F155)</f>
         <v/>
@@ -4815,7 +5313,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F156" s="2" t="n"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>de Brahma</t>
+        </is>
+      </c>
       <c r="G156" s="3">
         <f>IF(F156="","","Técnica Sólida "&amp;F156)</f>
         <v/>
@@ -4845,7 +5347,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F157" s="2" t="n"/>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>do Trigrama Li</t>
+        </is>
+      </c>
       <c r="G157" s="3">
         <f>IF(F157="","","Técnica Sólida "&amp;F157)</f>
         <v/>
@@ -4875,7 +5381,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F158" s="2" t="n"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>do Astro</t>
+        </is>
+      </c>
       <c r="G158" s="3">
         <f>IF(F158="","","Técnica Sólida "&amp;F158)</f>
         <v/>
@@ -4905,7 +5415,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F159" s="2" t="n"/>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>dos Nove</t>
+        </is>
+      </c>
       <c r="G159" s="3">
         <f>IF(F159="","","Técnica Sólida "&amp;F159)</f>
         <v/>
@@ -4935,7 +5449,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F160" s="2" t="n"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>do Caos</t>
+        </is>
+      </c>
       <c r="G160" s="3">
         <f>IF(F160="","","Técnica Sólida "&amp;F160)</f>
         <v/>
@@ -4965,7 +5483,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F161" s="2" t="n"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>do Pilar</t>
+        </is>
+      </c>
       <c r="G161" s="3">
         <f>IF(F161="","","Técnica Sólida "&amp;F161)</f>
         <v/>
@@ -4995,7 +5517,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F162" s="2" t="n"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>da Verdade</t>
+        </is>
+      </c>
       <c r="G162" s="3">
         <f>IF(F162="","","Técnica Sólida "&amp;F162)</f>
         <v/>
@@ -5025,7 +5551,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F163" s="2" t="n"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>da Imaculada</t>
+        </is>
+      </c>
       <c r="G163" s="3">
         <f>IF(F163="","","Técnica Sólida "&amp;F163)</f>
         <v/>
@@ -5055,7 +5585,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F164" s="2" t="n"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>da Essência</t>
+        </is>
+      </c>
       <c r="G164" s="3">
         <f>IF(F164="","","Técnica Sólida "&amp;F164)</f>
         <v/>
@@ -5085,7 +5619,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F165" s="2" t="n"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>da Ponta</t>
+        </is>
+      </c>
       <c r="G165" s="3">
         <f>IF(F165="","","Técnica Sólida "&amp;F165)</f>
         <v/>
@@ -5115,7 +5653,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F166" s="2" t="n"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>do Regresso</t>
+        </is>
+      </c>
       <c r="G166" s="3">
         <f>IF(F166="","","Técnica Sólida "&amp;F166)</f>
         <v/>
@@ -5145,7 +5687,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F167" s="2" t="n"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>da Dualidade</t>
+        </is>
+      </c>
       <c r="G167" s="3">
         <f>IF(F167="","","Técnica Sólida "&amp;F167)</f>
         <v/>
@@ -5175,7 +5721,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F168" s="2" t="n"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>do Único</t>
+        </is>
+      </c>
       <c r="G168" s="3">
         <f>IF(F168="","","Técnica Sólida "&amp;F168)</f>
         <v/>
@@ -5205,7 +5755,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F169" s="2" t="n"/>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>da Flutuação</t>
+        </is>
+      </c>
       <c r="G169" s="3">
         <f>IF(F169="","","Técnica Sólida "&amp;F169)</f>
         <v/>
@@ -5235,7 +5789,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F170" s="2" t="n"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>da Miríade</t>
+        </is>
+      </c>
       <c r="G170" s="3">
         <f>IF(F170="","","Técnica Sólida "&amp;F170)</f>
         <v/>
@@ -5265,7 +5823,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F171" s="2" t="n"/>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>das Cinzas</t>
+        </is>
+      </c>
       <c r="G171" s="3">
         <f>IF(F171="","","Técnica Sólida "&amp;F171)</f>
         <v/>
@@ -5295,7 +5857,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F172" s="2" t="n"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>da Absorção</t>
+        </is>
+      </c>
       <c r="G172" s="3">
         <f>IF(F172="","","Técnica Sólida "&amp;F172)</f>
         <v/>
@@ -5325,7 +5891,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F173" s="2" t="n"/>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>dos Três</t>
+        </is>
+      </c>
       <c r="G173" s="3">
         <f>IF(F173="","","Técnica Sólida "&amp;F173)</f>
         <v/>
@@ -5355,7 +5925,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F174" s="2" t="n"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>do Dao</t>
+        </is>
+      </c>
       <c r="G174" s="3">
         <f>IF(F174="","","Técnica Sólida "&amp;F174)</f>
         <v/>
@@ -5385,7 +5959,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F175" s="2" t="n"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>da Perversidade</t>
+        </is>
+      </c>
       <c r="G175" s="3">
         <f>IF(F175="","","Técnica Sólida "&amp;F175)</f>
         <v/>
@@ -5415,7 +5993,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F176" s="2" t="n"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>da Juventude</t>
+        </is>
+      </c>
       <c r="G176" s="3">
         <f>IF(F176="","","Técnica Sólida "&amp;F176)</f>
         <v/>
@@ -5445,7 +6027,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F177" s="2" t="n"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>do Resplendor</t>
+        </is>
+      </c>
       <c r="G177" s="3">
         <f>IF(F177="","","Técnica Sólida "&amp;F177)</f>
         <v/>
@@ -5475,7 +6061,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F178" s="2" t="n"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>do Vácuo Celeste</t>
+        </is>
+      </c>
       <c r="G178" s="3">
         <f>IF(F178="","","Técnica Sólida "&amp;F178)</f>
         <v/>
@@ -5505,7 +6095,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F179" s="2" t="n"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>da Forma</t>
+        </is>
+      </c>
       <c r="G179" s="3">
         <f>IF(F179="","","Técnica Sólida "&amp;F179)</f>
         <v/>
@@ -5535,7 +6129,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F180" s="2" t="n"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>da Esperança</t>
+        </is>
+      </c>
       <c r="G180" s="3">
         <f>IF(F180="","","Técnica Sólida "&amp;F180)</f>
         <v/>
@@ -5565,7 +6163,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F181" s="2" t="n"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>do Nirvana</t>
+        </is>
+      </c>
       <c r="G181" s="3">
         <f>IF(F181="","","Técnica Sólida "&amp;F181)</f>
         <v/>
@@ -5595,7 +6197,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F182" s="2" t="n"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>do Ardor</t>
+        </is>
+      </c>
       <c r="G182" s="3">
         <f>IF(F182="","","Técnica Sólida "&amp;F182)</f>
         <v/>
@@ -5625,7 +6231,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F183" s="2" t="n"/>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>da Gênese</t>
+        </is>
+      </c>
       <c r="G183" s="3">
         <f>IF(F183="","","Técnica Sólida "&amp;F183)</f>
         <v/>
@@ -5655,7 +6265,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F184" s="2" t="n"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>da Retidão</t>
+        </is>
+      </c>
       <c r="G184" s="3">
         <f>IF(F184="","","Técnica Sólida "&amp;F184)</f>
         <v/>
@@ -5685,7 +6299,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F185" s="2" t="n"/>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>do Lodo</t>
+        </is>
+      </c>
       <c r="G185" s="3">
         <f>IF(F185="","","Técnica Sólida "&amp;F185)</f>
         <v/>
@@ -5715,7 +6333,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F186" s="2" t="n"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>da Alvorada</t>
+        </is>
+      </c>
       <c r="G186" s="3">
         <f>IF(F186="","","Técnica Sólida "&amp;F186)</f>
         <v/>
@@ -5745,7 +6367,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F187" s="2" t="n"/>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>da Cisão</t>
+        </is>
+      </c>
       <c r="G187" s="3">
         <f>IF(F187="","","Técnica Sólida "&amp;F187)</f>
         <v/>
@@ -5775,7 +6401,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F188" s="2" t="n"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>da Dupla Forma</t>
+        </is>
+      </c>
       <c r="G188" s="3">
         <f>IF(F188="","","Técnica Sólida "&amp;F188)</f>
         <v/>
@@ -5805,7 +6435,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F189" s="2" t="n"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>do Passo</t>
+        </is>
+      </c>
       <c r="G189" s="3">
         <f>IF(F189="","","Técnica Sólida "&amp;F189)</f>
         <v/>
@@ -5835,7 +6469,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F190" s="2" t="n"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>da Obliteração</t>
+        </is>
+      </c>
       <c r="G190" s="3">
         <f>IF(F190="","","Técnica Sólida "&amp;F190)</f>
         <v/>
@@ -5865,7 +6503,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F191" s="2" t="n"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>da Ameaça</t>
+        </is>
+      </c>
       <c r="G191" s="3">
         <f>IF(F191="","","Técnica Sólida "&amp;F191)</f>
         <v/>
@@ -5895,7 +6537,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F192" s="2" t="n"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>da Bravura</t>
+        </is>
+      </c>
       <c r="G192" s="3">
         <f>IF(F192="","","Técnica Sólida "&amp;F192)</f>
         <v/>
@@ -5925,7 +6571,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F193" s="2" t="n"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>da Busca</t>
+        </is>
+      </c>
       <c r="G193" s="3">
         <f>IF(F193="","","Técnica Sólida "&amp;F193)</f>
         <v/>
@@ -5955,7 +6605,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F194" s="2" t="n"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>da Amarra</t>
+        </is>
+      </c>
       <c r="G194" s="3">
         <f>IF(F194="","","Técnica Sólida "&amp;F194)</f>
         <v/>
@@ -5985,7 +6639,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F195" s="2" t="n"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>da Dispersão</t>
+        </is>
+      </c>
       <c r="G195" s="3">
         <f>IF(F195="","","Técnica Sólida "&amp;F195)</f>
         <v/>
@@ -6015,7 +6673,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F196" s="2" t="n"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>da Liberdade</t>
+        </is>
+      </c>
       <c r="G196" s="3">
         <f>IF(F196="","","Técnica Sólida "&amp;F196)</f>
         <v/>
@@ -6045,7 +6707,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F197" s="2" t="n"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>do Véu</t>
+        </is>
+      </c>
       <c r="G197" s="3">
         <f>IF(F197="","","Técnica Sólida "&amp;F197)</f>
         <v/>
@@ -6075,7 +6741,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F198" s="2" t="n"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>dos Mil</t>
+        </is>
+      </c>
       <c r="G198" s="3">
         <f>IF(F198="","","Técnica Sólida "&amp;F198)</f>
         <v/>
@@ -6105,7 +6775,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F199" s="2" t="n"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>do Trigrama Qian</t>
+        </is>
+      </c>
       <c r="G199" s="3">
         <f>IF(F199="","","Técnica Sólida "&amp;F199)</f>
         <v/>
@@ -6135,7 +6809,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F200" s="2" t="n"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>dos Quatro</t>
+        </is>
+      </c>
       <c r="G200" s="3">
         <f>IF(F200="","","Técnica Sólida "&amp;F200)</f>
         <v/>
@@ -6165,7 +6843,11 @@
           <t>o inglês do jogo não segue o hanzi daqui em diante (lista desalinhada: pecados, virtudes etc.)</t>
         </is>
       </c>
-      <c r="F201" s="2" t="n"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>do Movimento</t>
+        </is>
+      </c>
       <c r="G201" s="3">
         <f>IF(F201="","","Técnica Sólida "&amp;F201)</f>
         <v/>
@@ -6190,10 +6872,8 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="6" max="7"/>
+    <col width="36" customWidth="1" min="8" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6262,9 +6942,16 @@
           <t>Clouded</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Nublada</t>
+        </is>
+      </c>
       <c r="H2" s="3">
         <f>IF(F2="","","Manual Secreto "&amp;F2&amp;" do Imortal")</f>
         <v/>
@@ -6293,9 +6980,16 @@
           <t>Feathered</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Plumado</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Plumada</t>
+        </is>
+      </c>
       <c r="H3" s="3">
         <f>IF(F3="","","Manual Secreto "&amp;F3&amp;" do Imortal")</f>
         <v/>
@@ -6324,9 +7018,16 @@
           <t>Drowned</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chuvoso</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Chuvosa</t>
+        </is>
+      </c>
       <c r="H4" s="3">
         <f>IF(F4="","","Manual Secreto "&amp;F4&amp;" do Imortal")</f>
         <v/>
@@ -6355,9 +7056,16 @@
           <t>Frozen</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Nevado</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
       <c r="H5" s="3">
         <f>IF(F5="","","Manual Secreto "&amp;F5&amp;" do Imortal")</f>
         <v/>
@@ -6386,9 +7094,16 @@
           <t>Petaled</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Florido</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
       <c r="H6" s="3">
         <f>IF(F6="","","Manual Secreto "&amp;F6&amp;" do Imortal")</f>
         <v/>
@@ -6417,8 +7132,11 @@
           <t>Starry</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Estelar</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="3">
         <f>IF(F7="","","Manual Secreto "&amp;F7&amp;" do Imortal")</f>
@@ -6448,8 +7166,11 @@
           <t>Moonlit</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Lunar</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="3">
         <f>IF(F8="","","Manual Secreto "&amp;F8&amp;" do Imortal")</f>
@@ -6479,8 +7200,11 @@
           <t>Cerulean</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Celeste</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="3">
         <f>IF(F9="","","Manual Secreto "&amp;F9&amp;" do Imortal")</f>
@@ -6510,9 +7234,16 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Vazio</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Vazia</t>
+        </is>
+      </c>
       <c r="H10" s="3">
         <f>IF(F10="","","Manual Secreto "&amp;F10&amp;" do Imortal")</f>
         <v/>
@@ -6541,9 +7272,16 @@
           <t>Ensouled</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Anímico</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Anímica</t>
+        </is>
+      </c>
       <c r="H11" s="3">
         <f>IF(F11="","","Manual Secreto "&amp;F11&amp;" do Imortal")</f>
         <v/>
@@ -6572,9 +7310,16 @@
           <t>Frosty</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Gélido</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Gélida</t>
+        </is>
+      </c>
       <c r="H12" s="3">
         <f>IF(F12="","","Manual Secreto "&amp;F12&amp;" do Imortal")</f>
         <v/>
@@ -6603,9 +7348,16 @@
           <t>Spirited</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Divino</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Divina</t>
+        </is>
+      </c>
       <c r="H13" s="3">
         <f>IF(F13="","","Manual Secreto "&amp;F13&amp;" do Imortal")</f>
         <v/>
@@ -6634,8 +7386,11 @@
           <t>Original</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Primordial</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="3">
         <f>IF(F14="","","Manual Secreto "&amp;F14&amp;" do Imortal")</f>
@@ -6665,9 +7420,16 @@
           <t>Airy</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Eóleo</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Eólea</t>
+        </is>
+      </c>
       <c r="H15" s="3">
         <f>IF(F15="","","Manual Secreto "&amp;F15&amp;" do Imortal")</f>
         <v/>
@@ -6696,8 +7458,11 @@
           <t>Sunny</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="3">
         <f>IF(F16="","","Manual Secreto "&amp;F16&amp;" do Imortal")</f>
@@ -6727,9 +7492,16 @@
           <t>Edged</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Escarpado</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Escarpada</t>
+        </is>
+      </c>
       <c r="H17" s="3">
         <f>IF(F17="","","Manual Secreto "&amp;F17&amp;" do Imortal")</f>
         <v/>
@@ -6758,8 +7530,11 @@
           <t>Nether</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Abissal</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="3">
         <f>IF(F18="","","Manual Secreto "&amp;F18&amp;" do Imortal")</f>
@@ -6789,8 +7564,11 @@
           <t>Ethereal</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Espiritual</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="3">
         <f>IF(F19="","","Manual Secreto "&amp;F19&amp;" do Imortal")</f>
@@ -6820,9 +7598,16 @@
           <t>Shadowy</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Sombrio</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Sombria</t>
+        </is>
+      </c>
       <c r="H20" s="3">
         <f>IF(F20="","","Manual Secreto "&amp;F20&amp;" do Imortal")</f>
         <v/>
@@ -6851,9 +7636,16 @@
           <t>Dusted</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Cinéreo</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Cinérea</t>
+        </is>
+      </c>
       <c r="H21" s="3">
         <f>IF(F21="","","Manual Secreto "&amp;F21&amp;" do Imortal")</f>
         <v/>
@@ -6882,9 +7674,16 @@
           <t>Chiming</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Sonoro</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="H22" s="3">
         <f>IF(F22="","","Manual Secreto "&amp;F22&amp;" do Imortal")</f>
         <v/>
@@ -6913,8 +7712,11 @@
           <t>Sunlit</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Radiante</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="3">
         <f>IF(F23="","","Manual Secreto "&amp;F23&amp;" do Imortal")</f>
@@ -6944,9 +7746,16 @@
           <t>Wounded</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Marcado</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Marcada</t>
+        </is>
+      </c>
       <c r="H24" s="3">
         <f>IF(F24="","","Manual Secreto "&amp;F24&amp;" do Imortal")</f>
         <v/>
@@ -6975,9 +7784,16 @@
           <t>Draconic</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Draconiano</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Draconiana</t>
+        </is>
+      </c>
       <c r="H25" s="3">
         <f>IF(F25="","","Manual Secreto "&amp;F25&amp;" do Imortal")</f>
         <v/>
@@ -7006,9 +7822,16 @@
           <t>Blooded</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Sanguinário</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Sanguinária</t>
+        </is>
+      </c>
       <c r="H26" s="3">
         <f>IF(F26="","","Manual Secreto "&amp;F26&amp;" do Imortal")</f>
         <v/>
@@ -7037,9 +7860,16 @@
           <t>Edgy</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Afiado</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Afiada</t>
+        </is>
+      </c>
       <c r="H27" s="3">
         <f>IF(F27="","","Manual Secreto "&amp;F27&amp;" do Imortal")</f>
         <v/>
@@ -7068,8 +7898,11 @@
           <t>Heartfelt</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Cordial</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="3">
         <f>IF(F28="","","Manual Secreto "&amp;F28&amp;" do Imortal")</f>
@@ -7099,9 +7932,16 @@
           <t>Hilly</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Montanhês</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Montanhesa</t>
+        </is>
+      </c>
       <c r="H29" s="3">
         <f>IF(F29="","","Manual Secreto "&amp;F29&amp;" do Imortal")</f>
         <v/>
@@ -7130,9 +7970,16 @@
           <t>Dark</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Obscuro</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Obscura</t>
+        </is>
+      </c>
       <c r="H30" s="3">
         <f>IF(F30="","","Manual Secreto "&amp;F30&amp;" do Imortal")</f>
         <v/>
@@ -7161,9 +8008,16 @@
           <t>Winged</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Alado</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Alada</t>
+        </is>
+      </c>
       <c r="H31" s="3">
         <f>IF(F31="","","Manual Secreto "&amp;F31&amp;" do Imortal")</f>
         <v/>
@@ -7192,9 +8046,16 @@
           <t>Dreamy</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Onírico</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Onírica</t>
+        </is>
+      </c>
       <c r="H32" s="3">
         <f>IF(F32="","","Manual Secreto "&amp;F32&amp;" do Imortal")</f>
         <v/>
@@ -7223,9 +8084,16 @@
           <t>Light</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Luminoso</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Luminosa</t>
+        </is>
+      </c>
       <c r="H33" s="3">
         <f>IF(F33="","","Manual Secreto "&amp;F33&amp;" do Imortal")</f>
         <v/>
@@ -7254,9 +8122,16 @@
           <t>Blooming</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Imaculado</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Imaculada</t>
+        </is>
+      </c>
       <c r="H34" s="3">
         <f>IF(F34="","","Manual Secreto "&amp;F34&amp;" do Imortal")</f>
         <v/>
@@ -7285,9 +8160,16 @@
           <t>Worldly</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Soberano</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Soberana</t>
+        </is>
+      </c>
       <c r="H35" s="3">
         <f>IF(F35="","","Manual Secreto "&amp;F35&amp;" do Imortal")</f>
         <v/>
@@ -7316,9 +8198,16 @@
           <t>Demonic</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Demoníaco</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Demoníaca</t>
+        </is>
+      </c>
       <c r="H36" s="3">
         <f>IF(F36="","","Manual Secreto "&amp;F36&amp;" do Imortal")</f>
         <v/>
@@ -7347,9 +8236,16 @@
           <t>Cawing</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Corvino</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Corvina</t>
+        </is>
+      </c>
       <c r="H37" s="3">
         <f>IF(F37="","","Manual Secreto "&amp;F37&amp;" do Imortal")</f>
         <v/>
@@ -7378,8 +8274,11 @@
           <t>Binding</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" s="2" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Infernal</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="n"/>
       <c r="H38" s="3">
         <f>IF(F38="","","Manual Secreto "&amp;F38&amp;" do Imortal")</f>
@@ -7409,9 +8308,16 @@
           <t>Evil</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Maligno</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Maligna</t>
+        </is>
+      </c>
       <c r="H39" s="3">
         <f>IF(F39="","","Manual Secreto "&amp;F39&amp;" do Imortal")</f>
         <v/>
@@ -7440,8 +8346,11 @@
           <t>Smoky</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" s="2" t="n"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Fumegante</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="3">
         <f>IF(F40="","","Manual Secreto "&amp;F40&amp;" do Imortal")</f>
@@ -7471,9 +8380,16 @@
           <t>Inky</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Tingido</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Tingida</t>
+        </is>
+      </c>
       <c r="H41" s="3">
         <f>IF(F41="","","Manual Secreto "&amp;F41&amp;" do Imortal")</f>
         <v/>
@@ -7502,8 +8418,11 @@
           <t>Thundrous</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" s="2" t="n"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Trovejante</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="3">
         <f>IF(F42="","","Manual Secreto "&amp;F42&amp;" do Imortal")</f>
@@ -7533,9 +8452,16 @@
           <t>Cherry</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Rosado</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Rosada</t>
+        </is>
+      </c>
       <c r="H43" s="3">
         <f>IF(F43="","","Manual Secreto "&amp;F43&amp;" do Imortal")</f>
         <v/>
@@ -7564,9 +8490,16 @@
           <t>Nightly</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Noturno</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Noturna</t>
+        </is>
+      </c>
       <c r="H44" s="3">
         <f>IF(F44="","","Manual Secreto "&amp;F44&amp;" do Imortal")</f>
         <v/>
@@ -7595,9 +8528,16 @@
           <t>Jade</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Precioso</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Preciosa</t>
+        </is>
+      </c>
       <c r="H45" s="3">
         <f>IF(F45="","","Manual Secreto "&amp;F45&amp;" do Imortal")</f>
         <v/>
@@ -7626,9 +8566,16 @@
           <t>Cold</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Frígido</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Frígida</t>
+        </is>
+      </c>
       <c r="H46" s="3">
         <f>IF(F46="","","Manual Secreto "&amp;F46&amp;" do Imortal")</f>
         <v/>
@@ -7657,9 +8604,16 @@
           <t>Menacing</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Funesto</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Funesta</t>
+        </is>
+      </c>
       <c r="H47" s="3">
         <f>IF(F47="","","Manual Secreto "&amp;F47&amp;" do Imortal")</f>
         <v/>
@@ -7688,9 +8642,16 @@
           <t>Stony</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Rochoso</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Rochosa</t>
+        </is>
+      </c>
       <c r="H48" s="3">
         <f>IF(F48="","","Manual Secreto "&amp;F48&amp;" do Imortal")</f>
         <v/>
@@ -7719,9 +8680,16 @@
           <t>Truthful</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Sagrado</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Sagrada</t>
+        </is>
+      </c>
       <c r="H49" s="3">
         <f>IF(F49="","","Manual Secreto "&amp;F49&amp;" do Imortal")</f>
         <v/>
@@ -7750,9 +8718,16 @@
           <t>Tigris</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Tigrino</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Tigrina</t>
+        </is>
+      </c>
       <c r="H50" s="3">
         <f>IF(F50="","","Manual Secreto "&amp;F50&amp;" do Imortal")</f>
         <v/>
@@ -7781,9 +8756,16 @@
           <t>High</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Altaneiro</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Altaneira</t>
+        </is>
+      </c>
       <c r="H51" s="3">
         <f>IF(F51="","","Manual Secreto "&amp;F51&amp;" do Imortal")</f>
         <v/>
@@ -7812,9 +8794,16 @@
           <t>Hearty</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Vigoroso</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Vigorosa</t>
+        </is>
+      </c>
       <c r="H52" s="3">
         <f>IF(F52="","","Manual Secreto "&amp;F52&amp;" do Imortal")</f>
         <v/>
@@ -7843,9 +8832,16 @@
           <t>Miasmic</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Miasmático</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Miasmática</t>
+        </is>
+      </c>
       <c r="H53" s="3">
         <f>IF(F53="","","Manual Secreto "&amp;F53&amp;" do Imortal")</f>
         <v/>
@@ -7874,9 +8870,16 @@
           <t>Balanced</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Equilibrado</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Equilibrada</t>
+        </is>
+      </c>
       <c r="H54" s="3">
         <f>IF(F54="","","Manual Secreto "&amp;F54&amp;" do Imortal")</f>
         <v/>
@@ -7905,9 +8908,16 @@
           <t>Veiled</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="n"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Oculto</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Oculta</t>
+        </is>
+      </c>
       <c r="H55" s="3">
         <f>IF(F55="","","Manual Secreto "&amp;F55&amp;" do Imortal")</f>
         <v/>
@@ -7936,9 +8946,16 @@
           <t>Trying</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Calamitoso</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Calamitosa</t>
+        </is>
+      </c>
       <c r="H56" s="3">
         <f>IF(F56="","","Manual Secreto "&amp;F56&amp;" do Imortal")</f>
         <v/>
@@ -7967,9 +8984,16 @@
           <t>Forming</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Físico</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Física</t>
+        </is>
+      </c>
       <c r="H57" s="3">
         <f>IF(F57="","","Manual Secreto "&amp;F57&amp;" do Imortal")</f>
         <v/>
@@ -7998,9 +9022,16 @@
           <t>Deep</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Profundo</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Profunda</t>
+        </is>
+      </c>
       <c r="H58" s="3">
         <f>IF(F58="","","Manual Secreto "&amp;F58&amp;" do Imortal")</f>
         <v/>
@@ -8029,9 +9060,16 @@
           <t>Divine</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Santo</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Santa</t>
+        </is>
+      </c>
       <c r="H59" s="3">
         <f>IF(F59="","","Manual Secreto "&amp;F59&amp;" do Imortal")</f>
         <v/>
@@ -8060,8 +9098,11 @@
           <t>Ghostly</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" s="2" t="n"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Espectral</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="3">
         <f>IF(F60="","","Manual Secreto "&amp;F60&amp;" do Imortal")</f>
@@ -8091,9 +9132,16 @@
           <t>Shiny</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Cristalino</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Cristalina</t>
+        </is>
+      </c>
       <c r="H61" s="3">
         <f>IF(F61="","","Manual Secreto "&amp;F61&amp;" do Imortal")</f>
         <v/>
@@ -8122,9 +9170,16 @@
           <t>Lofty</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Empíreo</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Empírea</t>
+        </is>
+      </c>
       <c r="H62" s="3">
         <f>IF(F62="","","Manual Secreto "&amp;F62&amp;" do Imortal")</f>
         <v/>
@@ -8153,8 +9208,11 @@
           <t>Pulsing</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" s="2" t="n"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Pulsante</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="n"/>
       <c r="H63" s="3">
         <f>IF(F63="","","Manual Secreto "&amp;F63&amp;" do Imortal")</f>
@@ -8184,8 +9242,11 @@
           <t>Dancing</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" s="2" t="n"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Dançante</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="n"/>
       <c r="H64" s="3">
         <f>IF(F64="","","Manual Secreto "&amp;F64&amp;" do Imortal")</f>
@@ -8215,8 +9276,11 @@
           <t>Gleaming</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" s="2" t="n"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Cintilante</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="3">
         <f>IF(F65="","","Manual Secreto "&amp;F65&amp;" do Imortal")</f>
@@ -8246,8 +9310,11 @@
           <t>Diving</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" s="2" t="n"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Cadente</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="3">
         <f>IF(F66="","","Manual Secreto "&amp;F66&amp;" do Imortal")</f>
@@ -8277,8 +9344,11 @@
           <t>Drifting</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" s="2" t="n"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Flutuante</t>
+        </is>
+      </c>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="3">
         <f>IF(F67="","","Manual Secreto "&amp;F67&amp;" do Imortal")</f>
@@ -8308,9 +9378,16 @@
           <t>Focusing</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" s="2" t="n"/>
-      <c r="G68" s="2" t="n"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Condensado</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Condensada</t>
+        </is>
+      </c>
       <c r="H68" s="3">
         <f>IF(F68="","","Manual Secreto "&amp;F68&amp;" do Imortal")</f>
         <v/>
@@ -8339,9 +9416,16 @@
           <t>Pure</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Límpido</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Límpida</t>
+        </is>
+      </c>
       <c r="H69" s="3">
         <f>IF(F69="","","Manual Secreto "&amp;F69&amp;" do Imortal")</f>
         <v/>
@@ -8370,9 +9454,16 @@
           <t>Deathly</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Aniquilador</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Aniquiladora</t>
+        </is>
+      </c>
       <c r="H70" s="3">
         <f>IF(F70="","","Manual Secreto "&amp;F70&amp;" do Imortal")</f>
         <v/>
@@ -8401,8 +9492,11 @@
           <t>Gliding</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Transiente</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="3">
         <f>IF(F71="","","Manual Secreto "&amp;F71&amp;" do Imortal")</f>
@@ -8432,9 +9526,16 @@
           <t>Roaring</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Ruidoso</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Ruidosa</t>
+        </is>
+      </c>
       <c r="H72" s="3">
         <f>IF(F72="","","Manual Secreto "&amp;F72&amp;" do Imortal")</f>
         <v/>
@@ -8463,8 +9564,11 @@
           <t>Chilling</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" s="2" t="n"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Algente</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="3">
         <f>IF(F73="","","Manual Secreto "&amp;F73&amp;" do Imortal")</f>
@@ -8494,9 +9598,16 @@
           <t>Flawed</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Maculado</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Maculada</t>
+        </is>
+      </c>
       <c r="H74" s="3">
         <f>IF(F74="","","Manual Secreto "&amp;F74&amp;" do Imortal")</f>
         <v/>
@@ -8525,8 +9636,11 @@
           <t>Prismic</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" s="2" t="n"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Iridescente</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="3">
         <f>IF(F75="","","Manual Secreto "&amp;F75&amp;" do Imortal")</f>
@@ -8556,9 +9670,16 @@
           <t>Thinking</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" s="2" t="n"/>
-      <c r="G76" s="2" t="n"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Pensativo</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Pensativa</t>
+        </is>
+      </c>
       <c r="H76" s="3">
         <f>IF(F76="","","Manual Secreto "&amp;F76&amp;" do Imortal")</f>
         <v/>
@@ -8587,9 +9708,16 @@
           <t>Blue</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" s="2" t="n"/>
-      <c r="G77" s="2" t="n"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Vasto</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Vasta</t>
+        </is>
+      </c>
       <c r="H77" s="3">
         <f>IF(F77="","","Manual Secreto "&amp;F77&amp;" do Imortal")</f>
         <v/>
@@ -8618,9 +9746,16 @@
           <t>Stormy</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" s="2" t="n"/>
-      <c r="G78" s="2" t="n"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Nevoento</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Nevoenta</t>
+        </is>
+      </c>
       <c r="H78" s="3">
         <f>IF(F78="","","Manual Secreto "&amp;F78&amp;" do Imortal")</f>
         <v/>
@@ -8649,9 +9784,16 @@
           <t>Ruinous</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Quebrado</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Quebrada</t>
+        </is>
+      </c>
       <c r="H79" s="3">
         <f>IF(F79="","","Manual Secreto "&amp;F79&amp;" do Imortal")</f>
         <v/>
@@ -8680,9 +9822,16 @@
           <t>Breaking</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" s="2" t="n"/>
-      <c r="G80" s="2" t="n"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Despedaçado</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Despedaçada</t>
+        </is>
+      </c>
       <c r="H80" s="3">
         <f>IF(F80="","","Manual Secreto "&amp;F80&amp;" do Imortal")</f>
         <v/>
@@ -8711,8 +9860,11 @@
           <t>Becoming</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" s="2" t="n"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Mutável</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="3">
         <f>IF(F81="","","Manual Secreto "&amp;F81&amp;" do Imortal")</f>
@@ -8742,9 +9894,16 @@
           <t>Misty</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Enevoado</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Enevoada</t>
+        </is>
+      </c>
       <c r="H82" s="3">
         <f>IF(F82="","","Manual Secreto "&amp;F82&amp;" do Imortal")</f>
         <v/>
@@ -8773,8 +9932,11 @@
           <t>Singing</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" s="2" t="n"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Cantante</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="n"/>
       <c r="H83" s="3">
         <f>IF(F83="","","Manual Secreto "&amp;F83&amp;" do Imortal")</f>
@@ -8804,9 +9966,16 @@
           <t>Decaying</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Ermo</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Erma</t>
+        </is>
+      </c>
       <c r="H84" s="3">
         <f>IF(F84="","","Manual Secreto "&amp;F84&amp;" do Imortal")</f>
         <v/>
@@ -8835,9 +10004,16 @@
           <t>Falling</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" s="2" t="n"/>
-      <c r="G85" s="2" t="n"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Meteórico</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Meteórica</t>
+        </is>
+      </c>
       <c r="H85" s="3">
         <f>IF(F85="","","Manual Secreto "&amp;F85&amp;" do Imortal")</f>
         <v/>
@@ -8866,9 +10042,16 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Mundano</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Mundana</t>
+        </is>
+      </c>
       <c r="H86" s="3">
         <f>IF(F86="","","Manual Secreto "&amp;F86&amp;" do Imortal")</f>
         <v/>
@@ -8897,9 +10080,16 @@
           <t>Voidborn</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" s="2" t="n"/>
-      <c r="G87" s="2" t="n"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Vacuoso</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Vacuosa</t>
+        </is>
+      </c>
       <c r="H87" s="3">
         <f>IF(F87="","","Manual Secreto "&amp;F87&amp;" do Imortal")</f>
         <v/>
@@ -8928,9 +10118,16 @@
           <t>Sandy</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" s="2" t="n"/>
-      <c r="G88" s="2" t="n"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Arenoso</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Arenosa</t>
+        </is>
+      </c>
       <c r="H88" s="3">
         <f>IF(F88="","","Manual Secreto "&amp;F88&amp;" do Imortal")</f>
         <v/>
@@ -8959,9 +10156,16 @@
           <t>Tidal</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" s="2" t="n"/>
-      <c r="G89" s="2" t="n"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Agitado</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Agitada</t>
+        </is>
+      </c>
       <c r="H89" s="3">
         <f>IF(F89="","","Manual Secreto "&amp;F89&amp;" do Imortal")</f>
         <v/>
@@ -8990,8 +10194,11 @@
           <t>Wavy</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" s="2" t="n"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Ondulante</t>
+        </is>
+      </c>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="3">
         <f>IF(F90="","","Manual Secreto "&amp;F90&amp;" do Imortal")</f>
@@ -9026,8 +10233,16 @@
           <t>o inglês diz 'Moist', o hanzi é 'onda'</t>
         </is>
       </c>
-      <c r="F91" s="2" t="n"/>
-      <c r="G91" s="2" t="n"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Sinuoso</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Sinuosa</t>
+        </is>
+      </c>
       <c r="H91" s="3">
         <f>IF(F91="","","Manual Secreto "&amp;F91&amp;" do Imortal")</f>
         <v/>
@@ -9056,9 +10271,16 @@
           <t>Rippling</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Avassalador</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Avassaladora</t>
+        </is>
+      </c>
       <c r="H92" s="3">
         <f>IF(F92="","","Manual Secreto "&amp;F92&amp;" do Imortal")</f>
         <v/>
@@ -9087,9 +10309,16 @@
           <t>Gloomy</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" s="2" t="n"/>
-      <c r="G93" s="2" t="n"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Tenebroso</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Tenebrosa</t>
+        </is>
+      </c>
       <c r="H93" s="3">
         <f>IF(F93="","","Manual Secreto "&amp;F93&amp;" do Imortal")</f>
         <v/>
@@ -9118,8 +10347,11 @@
           <t>Dawning</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" s="2" t="n"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Astral</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="3">
         <f>IF(F94="","","Manual Secreto "&amp;F94&amp;" do Imortal")</f>
@@ -9149,9 +10381,16 @@
           <t>Bridged</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" s="2" t="n"/>
-      <c r="G95" s="2" t="n"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Elevado</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Elevada</t>
+        </is>
+      </c>
       <c r="H95" s="3">
         <f>IF(F95="","","Manual Secreto "&amp;F95&amp;" do Imortal")</f>
         <v/>
@@ -9180,9 +10419,16 @@
           <t>Valley</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="2" t="n"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Cavo</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Cava</t>
+        </is>
+      </c>
       <c r="H96" s="3">
         <f>IF(F96="","","Manual Secreto "&amp;F96&amp;" do Imortal")</f>
         <v/>
@@ -9211,9 +10457,16 @@
           <t>Steep</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="2" t="n"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Abrupto</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Abrupta</t>
+        </is>
+      </c>
       <c r="H97" s="3">
         <f>IF(F97="","","Manual Secreto "&amp;F97&amp;" do Imortal")</f>
         <v/>
@@ -9242,9 +10495,16 @@
           <t>Peaked</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="2" t="n"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Pontiagudo</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Pontiaguda</t>
+        </is>
+      </c>
       <c r="H98" s="3">
         <f>IF(F98="","","Manual Secreto "&amp;F98&amp;" do Imortal")</f>
         <v/>
@@ -9278,7 +10538,11 @@
           <t>o inglês diz 'Streaming', o hanzi é 'lago'</t>
         </is>
       </c>
-      <c r="F99" s="2" t="n"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Lacustre</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="3">
         <f>IF(F99="","","Manual Secreto "&amp;F99&amp;" do Imortal")</f>
@@ -9308,8 +10572,11 @@
           <t>Flowing</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" s="2" t="n"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Fluvial</t>
+        </is>
+      </c>
       <c r="G100" s="2" t="n"/>
       <c r="H100" s="3">
         <f>IF(F100="","","Manual Secreto "&amp;F100&amp;" do Imortal")</f>
@@ -9339,8 +10606,11 @@
           <t>River-run</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" s="2" t="n"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Corrente</t>
+        </is>
+      </c>
       <c r="G101" s="2" t="n"/>
       <c r="H101" s="3">
         <f>IF(F101="","","Manual Secreto "&amp;F101&amp;" do Imortal")</f>
@@ -9370,8 +10640,11 @@
           <t>Engulfing</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" s="2" t="n"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Torrencial</t>
+        </is>
+      </c>
       <c r="G102" s="2" t="n"/>
       <c r="H102" s="3">
         <f>IF(F102="","","Manual Secreto "&amp;F102&amp;" do Imortal")</f>
@@ -9401,9 +10674,16 @@
           <t>Oceanic</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="n"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Marinho</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Marinha</t>
+        </is>
+      </c>
       <c r="H103" s="3">
         <f>IF(F103="","","Manual Secreto "&amp;F103&amp;" do Imortal")</f>
         <v/>
@@ -9432,9 +10712,16 @@
           <t>Symbolic</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="n"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Selado</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Selada</t>
+        </is>
+      </c>
       <c r="H104" s="3">
         <f>IF(F104="","","Manual Secreto "&amp;F104&amp;" do Imortal")</f>
         <v/>
@@ -9463,8 +10750,11 @@
           <t>Tolling</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" s="2" t="n"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Ecoante</t>
+        </is>
+      </c>
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="3">
         <f>IF(F105="","","Manual Secreto "&amp;F105&amp;" do Imortal")</f>
@@ -9494,9 +10784,16 @@
           <t>Vesseled</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Ritualístico</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Ritualística</t>
+        </is>
+      </c>
       <c r="H106" s="3">
         <f>IF(F106="","","Manual Secreto "&amp;F106&amp;" do Imortal")</f>
         <v/>
@@ -9525,9 +10822,16 @@
           <t>Marvelous</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Ilusório</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Ilusória</t>
+        </is>
+      </c>
       <c r="H107" s="3">
         <f>IF(F107="","","Manual Secreto "&amp;F107&amp;" do Imortal")</f>
         <v/>
@@ -9556,8 +10860,11 @@
           <t>Daemonic</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" s="2" t="n"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Feroz</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="3">
         <f>IF(F108="","","Manual Secreto "&amp;F108&amp;" do Imortal")</f>
@@ -9587,8 +10894,11 @@
           <t>Immortal</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" s="2" t="n"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Imortal</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="3">
         <f>IF(F109="","","Manual Secreto "&amp;F109&amp;" do Imortal")</f>
@@ -9618,8 +10928,11 @@
           <t>Martial</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" s="2" t="n"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Marcial</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="3">
         <f>IF(F110="","","Manual Secreto "&amp;F110&amp;" do Imortal")</f>
@@ -9649,8 +10962,11 @@
           <t>Avian</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" s="2" t="n"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Veloz</t>
+        </is>
+      </c>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="3">
         <f>IF(F111="","","Manual Secreto "&amp;F111&amp;" do Imortal")</f>
@@ -9685,8 +11001,16 @@
           <t>o inglês diz 'Ironic', o hanzi é 'firme'</t>
         </is>
       </c>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="2" t="n"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Rígido</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Rígida</t>
+        </is>
+      </c>
       <c r="H112" s="3">
         <f>IF(F112="","","Manual Secreto "&amp;F112&amp;" do Imortal")</f>
         <v/>
@@ -9715,9 +11039,16 @@
           <t>Sweeping</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" s="2" t="n"/>
-      <c r="G113" s="2" t="n"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Varredor</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Varredora</t>
+        </is>
+      </c>
       <c r="H113" s="3">
         <f>IF(F113="","","Manual Secreto "&amp;F113&amp;" do Imortal")</f>
         <v/>
@@ -9746,8 +11077,11 @@
           <t>Rear</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" s="2" t="n"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Dorsal</t>
+        </is>
+      </c>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="3">
         <f>IF(F114="","","Manual Secreto "&amp;F114&amp;" do Imortal")</f>
@@ -9777,8 +11111,11 @@
           <t>Earthly</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" s="2" t="n"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Terrestre</t>
+        </is>
+      </c>
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="3">
         <f>IF(F115="","","Manual Secreto "&amp;F115&amp;" do Imortal")</f>
@@ -9808,9 +11145,16 @@
           <t>Bodily</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" s="2" t="n"/>
-      <c r="G116" s="2" t="n"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Corpóreo</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Corpórea</t>
+        </is>
+      </c>
       <c r="H116" s="3">
         <f>IF(F116="","","Manual Secreto "&amp;F116&amp;" do Imortal")</f>
         <v/>
@@ -9839,8 +11183,11 @@
           <t>Wild</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" s="2" t="n"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Selvagem</t>
+        </is>
+      </c>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="3">
         <f>IF(F117="","","Manual Secreto "&amp;F117&amp;" do Imortal")</f>
@@ -9870,9 +11217,16 @@
           <t>Moving</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Movediço</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Movediça</t>
+        </is>
+      </c>
       <c r="H118" s="3">
         <f>IF(F118="","","Manual Secreto "&amp;F118&amp;" do Imortal")</f>
         <v/>
@@ -9901,9 +11255,16 @@
           <t>Shelled</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" s="2" t="n"/>
-      <c r="G119" s="2" t="n"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Encouraçado</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Encouraçada</t>
+        </is>
+      </c>
       <c r="H119" s="3">
         <f>IF(F119="","","Manual Secreto "&amp;F119&amp;" do Imortal")</f>
         <v/>
@@ -9932,9 +11293,16 @@
           <t>Perilous</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="2" t="n"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Perverso</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Perversa</t>
+        </is>
+      </c>
       <c r="H120" s="3">
         <f>IF(F120="","","Manual Secreto "&amp;F120&amp;" do Imortal")</f>
         <v/>
@@ -9963,9 +11331,16 @@
           <t>Wise</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" s="2" t="n"/>
-      <c r="G121" s="2" t="n"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Heroico</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Heroica</t>
+        </is>
+      </c>
       <c r="H121" s="3">
         <f>IF(F121="","","Manual Secreto "&amp;F121&amp;" do Imortal")</f>
         <v/>
@@ -9994,9 +11369,16 @@
           <t>Maple</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" s="2" t="n"/>
-      <c r="G122" s="2" t="n"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Acobreado</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Acobreada</t>
+        </is>
+      </c>
       <c r="H122" s="3">
         <f>IF(F122="","","Manual Secreto "&amp;F122&amp;" do Imortal")</f>
         <v/>
@@ -10025,9 +11407,16 @@
           <t>Anserine</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" s="2" t="n"/>
-      <c r="G123" s="2" t="n"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Migratório</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Migratória</t>
+        </is>
+      </c>
       <c r="H123" s="3">
         <f>IF(F123="","","Manual Secreto "&amp;F123&amp;" do Imortal")</f>
         <v/>
@@ -10056,8 +11445,11 @@
           <t>Hazy</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" s="2" t="n"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Crepuscular</t>
+        </is>
+      </c>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="3">
         <f>IF(F124="","","Manual Secreto "&amp;F124&amp;" do Imortal")</f>
@@ -10092,8 +11484,16 @@
           <t>o inglês diz 'Windy', o hanzi é 'fênix'</t>
         </is>
       </c>
-      <c r="F125" s="2" t="n"/>
-      <c r="G125" s="2" t="n"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Renascido</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Renascida</t>
+        </is>
+      </c>
       <c r="H125" s="3">
         <f>IF(F125="","","Manual Secreto "&amp;F125&amp;" do Imortal")</f>
         <v/>
@@ -10122,9 +11522,16 @@
           <t>United</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Unido</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Unida</t>
+        </is>
+      </c>
       <c r="H126" s="3">
         <f>IF(F126="","","Manual Secreto "&amp;F126&amp;" do Imortal")</f>
         <v/>
@@ -10153,9 +11560,16 @@
           <t>Lonely</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" s="2" t="n"/>
-      <c r="G127" s="2" t="n"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Solitário</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Solitária</t>
+        </is>
+      </c>
       <c r="H127" s="3">
         <f>IF(F127="","","Manual Secreto "&amp;F127&amp;" do Imortal")</f>
         <v/>
@@ -10184,8 +11598,11 @@
           <t>Coming</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" s="2" t="n"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Iminente</t>
+        </is>
+      </c>
       <c r="G128" s="2" t="n"/>
       <c r="H128" s="3">
         <f>IF(F128="","","Manual Secreto "&amp;F128&amp;" do Imortal")</f>
@@ -10215,9 +11632,16 @@
           <t>Aspected</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" s="2" t="n"/>
-      <c r="G129" s="2" t="n"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Mútuo</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Mútua</t>
+        </is>
+      </c>
       <c r="H129" s="3">
         <f>IF(F129="","","Manual Secreto "&amp;F129&amp;" do Imortal")</f>
         <v/>
@@ -10246,8 +11670,11 @@
           <t>Forceful</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" s="2" t="n"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Celestial</t>
+        </is>
+      </c>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="3">
         <f>IF(F130="","","Manual Secreto "&amp;F130&amp;" do Imortal")</f>
@@ -10277,8 +11704,11 @@
           <t>Ritual</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" s="2" t="n"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Cerimonial</t>
+        </is>
+      </c>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="3">
         <f>IF(F131="","","Manual Secreto "&amp;F131&amp;" do Imortal")</f>
@@ -10308,8 +11738,11 @@
           <t>Phenomenal</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" s="2" t="n"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Fenomenal</t>
+        </is>
+      </c>
       <c r="G132" s="2" t="n"/>
       <c r="H132" s="3">
         <f>IF(F132="","","Manual Secreto "&amp;F132&amp;" do Imortal")</f>
@@ -10339,8 +11772,11 @@
           <t>Trigrammic</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" s="2" t="n"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Oracular</t>
+        </is>
+      </c>
       <c r="G133" s="2" t="n"/>
       <c r="H133" s="3">
         <f>IF(F133="","","Manual Secreto "&amp;F133&amp;" do Imortal")</f>
@@ -10370,8 +11806,11 @@
           <t>Military</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" s="2" t="n"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Militar</t>
+        </is>
+      </c>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="3">
         <f>IF(F134="","","Manual Secreto "&amp;F134&amp;" do Imortal")</f>
@@ -10401,9 +11840,16 @@
           <t>Mirroring</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" s="2" t="n"/>
-      <c r="G135" s="2" t="n"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Refletor</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Refletora</t>
+        </is>
+      </c>
       <c r="H135" s="3">
         <f>IF(F135="","","Manual Secreto "&amp;F135&amp;" do Imortal")</f>
         <v/>
@@ -10432,8 +11878,11 @@
           <t>Soft</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" s="2" t="n"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Suave</t>
+        </is>
+      </c>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="3">
         <f>IF(F136="","","Manual Secreto "&amp;F136&amp;" do Imortal")</f>
@@ -10463,9 +11912,16 @@
           <t>Peaceful</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" s="2" t="n"/>
-      <c r="G137" s="2" t="n"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Harmonioso</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Harmoniosa</t>
+        </is>
+      </c>
       <c r="H137" s="3">
         <f>IF(F137="","","Manual Secreto "&amp;F137&amp;" do Imortal")</f>
         <v/>
@@ -10494,9 +11950,16 @@
           <t>Signing</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" s="2" t="n"/>
-      <c r="G138" s="2" t="n"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Fechado</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Fechada</t>
+        </is>
+      </c>
       <c r="H138" s="3">
         <f>IF(F138="","","Manual Secreto "&amp;F138&amp;" do Imortal")</f>
         <v/>
@@ -10525,8 +11988,11 @@
           <t>Material</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" s="2" t="n"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Secular</t>
+        </is>
+      </c>
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="3">
         <f>IF(F139="","","Manual Secreto "&amp;F139&amp;" do Imortal")</f>
@@ -10556,9 +12022,16 @@
           <t>Ending</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" s="2" t="n"/>
-      <c r="G140" s="2" t="n"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Absoluto</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Absoluta</t>
+        </is>
+      </c>
       <c r="H140" s="3">
         <f>IF(F140="","","Manual Secreto "&amp;F140&amp;" do Imortal")</f>
         <v/>
@@ -10587,8 +12060,11 @@
           <t>Flaming</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" s="2" t="n"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Flamejante</t>
+        </is>
+      </c>
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="3">
         <f>IF(F141="","","Manual Secreto "&amp;F141&amp;" do Imortal")</f>
@@ -10618,8 +12094,11 @@
           <t>Bright</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" s="2" t="n"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Brilhante</t>
+        </is>
+      </c>
       <c r="G142" s="2" t="n"/>
       <c r="H142" s="3">
         <f>IF(F142="","","Manual Secreto "&amp;F142&amp;" do Imortal")</f>
@@ -10649,9 +12128,16 @@
           <t>Palatial</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" s="2" t="n"/>
-      <c r="G143" s="2" t="n"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Palaciano</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Palaciana</t>
+        </is>
+      </c>
       <c r="H143" s="3">
         <f>IF(F143="","","Manual Secreto "&amp;F143&amp;" do Imortal")</f>
         <v/>
@@ -10680,9 +12166,16 @@
           <t>Defected</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" s="2" t="n"/>
-      <c r="G144" s="2" t="n"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Mutilado</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Mutilada</t>
+        </is>
+      </c>
       <c r="H144" s="3">
         <f>IF(F144="","","Manual Secreto "&amp;F144&amp;" do Imortal")</f>
         <v/>
@@ -10711,9 +12204,16 @@
           <t>Walking</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" s="2" t="n"/>
-      <c r="G145" s="2" t="n"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Andarilho</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Andarilha</t>
+        </is>
+      </c>
       <c r="H145" s="3">
         <f>IF(F145="","","Manual Secreto "&amp;F145&amp;" do Imortal")</f>
         <v/>
@@ -10742,9 +12242,16 @@
           <t>Warring</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" s="2" t="n"/>
-      <c r="G146" s="2" t="n"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Bélico</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Bélica</t>
+        </is>
+      </c>
       <c r="H146" s="3">
         <f>IF(F146="","","Manual Secreto "&amp;F146&amp;" do Imortal")</f>
         <v/>
@@ -10773,9 +12280,16 @@
           <t>Killing</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" s="2" t="n"/>
-      <c r="G147" s="2" t="n"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Sanguinolento</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Sanguinolenta</t>
+        </is>
+      </c>
       <c r="H147" s="3">
         <f>IF(F147="","","Manual Secreto "&amp;F147&amp;" do Imortal")</f>
         <v/>
@@ -10804,8 +12318,11 @@
           <t>Bladed</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" s="2" t="n"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Cortante</t>
+        </is>
+      </c>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="3">
         <f>IF(F148="","","Manual Secreto "&amp;F148&amp;" do Imortal")</f>
@@ -10835,9 +12352,16 @@
           <t>Ultimate</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" s="2" t="n"/>
-      <c r="G149" s="2" t="n"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Máximo</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Máxima</t>
+        </is>
+      </c>
       <c r="H149" s="3">
         <f>IF(F149="","","Manual Secreto "&amp;F149&amp;" do Imortal")</f>
         <v/>
@@ -10866,8 +12390,11 @@
           <t>Cutting</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" s="2" t="n"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Perfurante</t>
+        </is>
+      </c>
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="3">
         <f>IF(F150="","","Manual Secreto "&amp;F150&amp;" do Imortal")</f>
@@ -10897,9 +12424,16 @@
           <t>Pearl</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" s="2" t="n"/>
-      <c r="G151" s="2" t="n"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Perolado</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Perolada</t>
+        </is>
+      </c>
       <c r="H151" s="3">
         <f>IF(F151="","","Manual Secreto "&amp;F151&amp;" do Imortal")</f>
         <v/>
@@ -10928,9 +12462,16 @@
           <t>Bundling</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" s="2" t="n"/>
-      <c r="G152" s="2" t="n"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Macio</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Macia</t>
+        </is>
+      </c>
       <c r="H152" s="3">
         <f>IF(F152="","","Manual Secreto "&amp;F152&amp;" do Imortal")</f>
         <v/>
@@ -10959,8 +12500,11 @@
           <t>Blinding</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" s="2" t="n"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Fuzilante</t>
+        </is>
+      </c>
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="3">
         <f>IF(F153="","","Manual Secreto "&amp;F153&amp;" do Imortal")</f>
@@ -10990,9 +12534,16 @@
           <t>Aerial</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" s="2" t="n"/>
-      <c r="G154" s="2" t="n"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Curvo</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Curva</t>
+        </is>
+      </c>
       <c r="H154" s="3">
         <f>IF(F154="","","Manual Secreto "&amp;F154&amp;" do Imortal")</f>
         <v/>
@@ -11021,9 +12572,16 @@
           <t>Combative</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" s="2" t="n"/>
-      <c r="G155" s="2" t="n"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Lutador</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Lutadora</t>
+        </is>
+      </c>
       <c r="H155" s="3">
         <f>IF(F155="","","Manual Secreto "&amp;F155&amp;" do Imortal")</f>
         <v/>
@@ -11057,8 +12615,16 @@
           <t>o inglês diz 'Only', o hanzi é 'verdadeiro'</t>
         </is>
       </c>
-      <c r="F156" s="2" t="n"/>
-      <c r="G156" s="2" t="n"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Verdadeira</t>
+        </is>
+      </c>
       <c r="H156" s="3">
         <f>IF(F156="","","Manual Secreto "&amp;F156&amp;" do Imortal")</f>
         <v/>
@@ -11092,8 +12658,16 @@
           <t>o inglês diz 'Knowing', o hanzi é 'véu, ignorância'</t>
         </is>
       </c>
-      <c r="F157" s="2" t="n"/>
-      <c r="G157" s="2" t="n"/>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Velado</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Velada</t>
+        </is>
+      </c>
       <c r="H157" s="3">
         <f>IF(F157="","","Manual Secreto "&amp;F157&amp;" do Imortal")</f>
         <v/>
@@ -11122,9 +12696,16 @@
           <t>Ivory</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" s="2" t="n"/>
-      <c r="G158" s="2" t="n"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Esmeraldino</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Esmeraldina</t>
+        </is>
+      </c>
       <c r="H158" s="3">
         <f>IF(F158="","","Manual Secreto "&amp;F158&amp;" do Imortal")</f>
         <v/>
@@ -11153,9 +12734,16 @@
           <t>Dusk</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" s="2" t="n"/>
-      <c r="G159" s="2" t="n"/>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Vespertino</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Vespertina</t>
+        </is>
+      </c>
       <c r="H159" s="3">
         <f>IF(F159="","","Manual Secreto "&amp;F159&amp;" do Imortal")</f>
         <v/>
@@ -11184,9 +12772,16 @@
           <t>Leafy</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" s="2" t="n"/>
-      <c r="G160" s="2" t="n"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Caduco</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Caduca</t>
+        </is>
+      </c>
       <c r="H160" s="3">
         <f>IF(F160="","","Manual Secreto "&amp;F160&amp;" do Imortal")</f>
         <v/>
@@ -11215,9 +12810,16 @@
           <t>Gnawing</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" s="2" t="n"/>
-      <c r="G161" s="2" t="n"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Corrosivo</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Corrosiva</t>
+        </is>
+      </c>
       <c r="H161" s="3">
         <f>IF(F161="","","Manual Secreto "&amp;F161&amp;" do Imortal")</f>
         <v/>
@@ -11246,8 +12848,11 @@
           <t>Willful</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" s="2" t="n"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Intencional</t>
+        </is>
+      </c>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="3">
         <f>IF(F162="","","Manual Secreto "&amp;F162&amp;" do Imortal")</f>
@@ -11277,9 +12882,16 @@
           <t>Deducing</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" s="2" t="n"/>
-      <c r="G163" s="2" t="n"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Derivado</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Derivada</t>
+        </is>
+      </c>
       <c r="H163" s="3">
         <f>IF(F163="","","Manual Secreto "&amp;F163&amp;" do Imortal")</f>
         <v/>
@@ -11313,8 +12925,16 @@
           <t>o inglês diz 'Umbral', o hanzi é 'pleno'</t>
         </is>
       </c>
-      <c r="F164" s="2" t="n"/>
-      <c r="G164" s="2" t="n"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Pleno</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Plena</t>
+        </is>
+      </c>
       <c r="H164" s="3">
         <f>IF(F164="","","Manual Secreto "&amp;F164&amp;" do Imortal")</f>
         <v/>
@@ -11343,8 +12963,11 @@
           <t>Loving</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" s="2" t="n"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Passional</t>
+        </is>
+      </c>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="3">
         <f>IF(F165="","","Manual Secreto "&amp;F165&amp;" do Imortal")</f>
@@ -11374,9 +12997,16 @@
           <t>Nacreous</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" s="2" t="n"/>
-      <c r="G166" s="2" t="n"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Adornado</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Adornada</t>
+        </is>
+      </c>
       <c r="H166" s="3">
         <f>IF(F166="","","Manual Secreto "&amp;F166&amp;" do Imortal")</f>
         <v/>
@@ -11405,9 +13035,16 @@
           <t>Silken</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" s="2" t="n"/>
-      <c r="G167" s="2" t="n"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Tecido</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Tecida</t>
+        </is>
+      </c>
       <c r="H167" s="3">
         <f>IF(F167="","","Manual Secreto "&amp;F167&amp;" do Imortal")</f>
         <v/>
@@ -11436,9 +13073,16 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" s="2" t="n"/>
-      <c r="G168" s="2" t="n"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Cósmico</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Cósmica</t>
+        </is>
+      </c>
       <c r="H168" s="3">
         <f>IF(F168="","","Manual Secreto "&amp;F168&amp;" do Imortal")</f>
         <v/>
@@ -11467,9 +13111,16 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" s="2" t="n"/>
-      <c r="G169" s="2" t="n"/>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Aquático</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Aquática</t>
+        </is>
+      </c>
       <c r="H169" s="3">
         <f>IF(F169="","","Manual Secreto "&amp;F169&amp;" do Imortal")</f>
         <v/>
@@ -11498,9 +13149,16 @@
           <t>Solid</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" s="2" t="n"/>
-      <c r="G170" s="2" t="n"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Maciço</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Maciça</t>
+        </is>
+      </c>
       <c r="H170" s="3">
         <f>IF(F170="","","Manual Secreto "&amp;F170&amp;" do Imortal")</f>
         <v/>
@@ -11529,9 +13187,16 @@
           <t>Mired</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" s="2" t="n"/>
-      <c r="G171" s="2" t="n"/>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Pantanoso</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Pantanosa</t>
+        </is>
+      </c>
       <c r="H171" s="3">
         <f>IF(F171="","","Manual Secreto "&amp;F171&amp;" do Imortal")</f>
         <v/>
@@ -11560,9 +13225,16 @@
           <t>Mystical</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" s="2" t="n"/>
-      <c r="G172" s="2" t="n"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Misterioso</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Misteriosa</t>
+        </is>
+      </c>
       <c r="H172" s="3">
         <f>IF(F172="","","Manual Secreto "&amp;F172&amp;" do Imortal")</f>
         <v/>
@@ -11591,9 +13263,16 @@
           <t>Birthing</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" s="2" t="n"/>
-      <c r="G173" s="2" t="n"/>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Viva</t>
+        </is>
+      </c>
       <c r="H173" s="3">
         <f>IF(F173="","","Manual Secreto "&amp;F173&amp;" do Imortal")</f>
         <v/>
@@ -11622,8 +13301,11 @@
           <t>First</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" s="2" t="n"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Inicial</t>
+        </is>
+      </c>
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="3">
         <f>IF(F174="","","Manual Secreto "&amp;F174&amp;" do Imortal")</f>
@@ -11653,8 +13335,11 @@
           <t>Key</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" s="2" t="n"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="3">
         <f>IF(F175="","","Manual Secreto "&amp;F175&amp;" do Imortal")</f>
@@ -11684,8 +13369,11 @@
           <t>Azure</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" s="2" t="n"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Anil</t>
+        </is>
+      </c>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="3">
         <f>IF(F176="","","Manual Secreto "&amp;F176&amp;" do Imortal")</f>
@@ -11715,9 +13403,16 @@
           <t>Cornering</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" s="2" t="n"/>
-      <c r="G177" s="2" t="n"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Curvado</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Curvada</t>
+        </is>
+      </c>
       <c r="H177" s="3">
         <f>IF(F177="","","Manual Secreto "&amp;F177&amp;" do Imortal")</f>
         <v/>
@@ -11746,9 +13441,16 @@
           <t>Powerful</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" s="2" t="n"/>
-      <c r="G178" s="2" t="n"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Autoritário</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Autoritária</t>
+        </is>
+      </c>
       <c r="H178" s="3">
         <f>IF(F178="","","Manual Secreto "&amp;F178&amp;" do Imortal")</f>
         <v/>
@@ -11777,9 +13479,16 @@
           <t>Forging</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" s="2" t="n"/>
-      <c r="G179" s="2" t="n"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Refinado</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Refinada</t>
+        </is>
+      </c>
       <c r="H179" s="3">
         <f>IF(F179="","","Manual Secreto "&amp;F179&amp;" do Imortal")</f>
         <v/>
@@ -11808,8 +13517,11 @@
           <t>Meteoric</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" s="2" t="n"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Perecível</t>
+        </is>
+      </c>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="3">
         <f>IF(F180="","","Manual Secreto "&amp;F180&amp;" do Imortal")</f>
@@ -11839,9 +13551,16 @@
           <t>Tainted</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" s="2" t="n"/>
-      <c r="G181" s="2" t="n"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Imundo</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Imunda</t>
+        </is>
+      </c>
       <c r="H181" s="3">
         <f>IF(F181="","","Manual Secreto "&amp;F181&amp;" do Imortal")</f>
         <v/>
@@ -11870,9 +13589,16 @@
           <t>Karmic</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" s="2" t="n"/>
-      <c r="G182" s="2" t="n"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Cármico</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Cármica</t>
+        </is>
+      </c>
       <c r="H182" s="3">
         <f>IF(F182="","","Manual Secreto "&amp;F182&amp;" do Imortal")</f>
         <v/>
@@ -11901,9 +13627,16 @@
           <t>Twin</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" s="2" t="n"/>
-      <c r="G183" s="2" t="n"/>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Duplo</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Dupla</t>
+        </is>
+      </c>
       <c r="H183" s="3">
         <f>IF(F183="","","Manual Secreto "&amp;F183&amp;" do Imortal")</f>
         <v/>
@@ -11932,9 +13665,16 @@
           <t>Tranquil</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" s="2" t="n"/>
-      <c r="G184" s="2" t="n"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Meditativo</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Meditativa</t>
+        </is>
+      </c>
       <c r="H184" s="3">
         <f>IF(F184="","","Manual Secreto "&amp;F184&amp;" do Imortal")</f>
         <v/>
@@ -11963,9 +13703,16 @@
           <t>Heaped</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" s="2" t="n"/>
-      <c r="G185" s="2" t="n"/>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Contido</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Contida</t>
+        </is>
+      </c>
       <c r="H185" s="3">
         <f>IF(F185="","","Manual Secreto "&amp;F185&amp;" do Imortal")</f>
         <v/>
@@ -11994,8 +13741,11 @@
           <t>Living</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" s="2" t="n"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Vital</t>
+        </is>
+      </c>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="3">
         <f>IF(F186="","","Manual Secreto "&amp;F186&amp;" do Imortal")</f>
@@ -12025,9 +13775,16 @@
           <t>Instant</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" s="2" t="n"/>
-      <c r="G187" s="2" t="n"/>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Efêmero</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Efêmera</t>
+        </is>
+      </c>
       <c r="H187" s="3">
         <f>IF(F187="","","Manual Secreto "&amp;F187&amp;" do Imortal")</f>
         <v/>
@@ -12056,9 +13813,16 @@
           <t>Adorned</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" s="2" t="n"/>
-      <c r="G188" s="2" t="n"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Estriado</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Estriada</t>
+        </is>
+      </c>
       <c r="H188" s="3">
         <f>IF(F188="","","Manual Secreto "&amp;F188&amp;" do Imortal")</f>
         <v/>
@@ -12087,8 +13851,11 @@
           <t>Burning</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" s="2" t="n"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Ardente</t>
+        </is>
+      </c>
       <c r="G189" s="2" t="n"/>
       <c r="H189" s="3">
         <f>IF(F189="","","Manual Secreto "&amp;F189&amp;" do Imortal")</f>
@@ -12118,9 +13885,16 @@
           <t>Plumed</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" s="2" t="n"/>
-      <c r="G190" s="2" t="n"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Plumoso</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Plumosa</t>
+        </is>
+      </c>
       <c r="H190" s="3">
         <f>IF(F190="","","Manual Secreto "&amp;F190&amp;" do Imortal")</f>
         <v/>
@@ -12149,9 +13923,16 @@
           <t>Alluring</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" s="2" t="n"/>
-      <c r="G191" s="2" t="n"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Sedutor</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Sedutora</t>
+        </is>
+      </c>
       <c r="H191" s="3">
         <f>IF(F191="","","Manual Secreto "&amp;F191&amp;" do Imortal")</f>
         <v/>
@@ -12180,9 +13961,16 @@
           <t>Minimal</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" s="2" t="n"/>
-      <c r="G192" s="2" t="n"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Diminuto</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Diminuta</t>
+        </is>
+      </c>
       <c r="H192" s="3">
         <f>IF(F192="","","Manual Secreto "&amp;F192&amp;" do Imortal")</f>
         <v/>
@@ -12211,8 +13999,11 @@
           <t>Spring</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" s="2" t="n"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Primaveril</t>
+        </is>
+      </c>
       <c r="G193" s="2" t="n"/>
       <c r="H193" s="3">
         <f>IF(F193="","","Manual Secreto "&amp;F193&amp;" do Imortal")</f>
@@ -12242,9 +14033,16 @@
           <t>Cardinal</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" s="2" t="n"/>
-      <c r="G194" s="2" t="n"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Grandioso</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Grandiosa</t>
+        </is>
+      </c>
       <c r="H194" s="3">
         <f>IF(F194="","","Manual Secreto "&amp;F194&amp;" do Imortal")</f>
         <v/>
@@ -12273,8 +14071,11 @@
           <t>Landed</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" s="2" t="n"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
       <c r="G195" s="2" t="n"/>
       <c r="H195" s="3">
         <f>IF(F195="","","Manual Secreto "&amp;F195&amp;" do Imortal")</f>
@@ -12304,9 +14105,16 @@
           <t>Windy</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" s="2" t="n"/>
-      <c r="G196" s="2" t="n"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Ventoso</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Ventosa</t>
+        </is>
+      </c>
       <c r="H196" s="3">
         <f>IF(F196="","","Manual Secreto "&amp;F196&amp;" do Imortal")</f>
         <v/>
@@ -12335,8 +14143,11 @@
           <t>Hailing</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" s="2" t="n"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Elegante</t>
+        </is>
+      </c>
       <c r="G197" s="2" t="n"/>
       <c r="H197" s="3">
         <f>IF(F197="","","Manual Secreto "&amp;F197&amp;" do Imortal")</f>
@@ -12366,8 +14177,11 @@
           <t>Southern</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" s="2" t="n"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Austral</t>
+        </is>
+      </c>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="3">
         <f>IF(F198="","","Manual Secreto "&amp;F198&amp;" do Imortal")</f>
@@ -12402,7 +14216,11 @@
           <t>o inglês diz 'Northern', o hanzi é 'leste'</t>
         </is>
       </c>
-      <c r="F199" s="2" t="n"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Oriental</t>
+        </is>
+      </c>
       <c r="G199" s="2" t="n"/>
       <c r="H199" s="3">
         <f>IF(F199="","","Manual Secreto "&amp;F199&amp;" do Imortal")</f>
@@ -12437,7 +14255,11 @@
           <t>o inglês diz 'Eastern', o hanzi é 'norte'</t>
         </is>
       </c>
-      <c r="F200" s="2" t="n"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Boreal</t>
+        </is>
+      </c>
       <c r="G200" s="2" t="n"/>
       <c r="H200" s="3">
         <f>IF(F200="","","Manual Secreto "&amp;F200&amp;" do Imortal")</f>
@@ -12467,8 +14289,11 @@
           <t>Autumnal</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" s="2" t="n"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Outonal</t>
+        </is>
+      </c>
       <c r="G201" s="2" t="n"/>
       <c r="H201" s="3">
         <f>IF(F201="","","Manual Secreto "&amp;F201&amp;" do Imortal")</f>
@@ -12494,14 +14319,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nome-base (já traduzido)</t>
@@ -13194,7 +15018,6 @@
           <t>落英</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>skill_name_middle10010</t>
@@ -13222,7 +15045,6 @@
           <t>落枫</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>skill_name_middle10020</t>
@@ -13250,7 +15072,6 @@
           <t>落雁</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>skill_name_middle10030</t>
@@ -13278,7 +15099,6 @@
           <t>落霞</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>skill_name_middle10040</t>
@@ -13434,7 +15254,6 @@
           <t>怒风</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>skill_name_middle10120</t>
@@ -13462,7 +15281,6 @@
           <t>暴风</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>skill_name_middle10130</t>
@@ -13490,7 +15308,6 @@
           <t>六迴</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>skill_name_middle10210</t>
@@ -13518,7 +15335,6 @@
           <t>八迴</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>skill_name_middle10220</t>
@@ -13546,7 +15362,6 @@
           <t>十迴</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>skill_name_middle10230</t>
@@ -13574,7 +15389,6 @@
           <t>火龙</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>skill_name_middle10310</t>
@@ -13602,7 +15416,6 @@
           <t>焰龙</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>skill_name_middle10320</t>
@@ -13630,7 +15443,6 @@
           <t>烛龙</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>skill_name_middle10330</t>
@@ -13658,7 +15470,6 @@
           <t>冰龙</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>skill_name_middle10410</t>
@@ -13686,7 +15497,6 @@
           <t>凛龙</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>skill_name_middle10420</t>
@@ -13714,7 +15524,6 @@
           <t>寒龙</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>skill_name_middle10430</t>
@@ -13742,7 +15551,6 @@
           <t>霜龙</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>skill_name_middle10440</t>
@@ -13770,7 +15578,6 @@
           <t>闪龙</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>skill_name_middle10510</t>
@@ -13798,7 +15605,6 @@
           <t>掣龙</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>skill_name_middle10520</t>
@@ -13826,7 +15632,6 @@
           <t>雷龙</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>skill_name_middle10530</t>
@@ -13854,7 +15659,6 @@
           <t>迅龙</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>skill_name_middle10540</t>
@@ -13882,7 +15686,6 @@
           <t>瞬龙</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>skill_name_middle10550</t>
@@ -13910,7 +15713,6 @@
           <t>卷龙</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>skill_name_middle10610</t>
@@ -13938,7 +15740,6 @@
           <t>驰龙</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>skill_name_middle10620</t>
@@ -13966,7 +15767,6 @@
           <t>石龙</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>skill_name_middle10710</t>
@@ -13994,7 +15794,6 @@
           <t>岩龙</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>skill_name_middle10720</t>
@@ -14022,7 +15821,6 @@
           <t>地龙</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>skill_name_middle10730</t>
@@ -14050,7 +15848,6 @@
           <t>震龙</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>skill_name_middle10740</t>
@@ -14078,7 +15875,6 @@
           <t>木龙</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>skill_name_middle10810</t>
@@ -14106,7 +15902,6 @@
           <t>藤龙</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>skill_name_middle10820</t>
@@ -14134,7 +15929,6 @@
           <t>棘龙</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>skill_name_middle10830</t>
@@ -14162,7 +15956,6 @@
           <t>破雾</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>skill_name_middle10910</t>
@@ -14190,7 +15983,6 @@
           <t>破空</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>skill_name_middle10920</t>
@@ -14218,7 +16010,6 @@
           <t>破天</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>skill_name_middle10930</t>
@@ -14246,7 +16037,6 @@
           <t>破界</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>skill_name_middle10940</t>
@@ -14754,7 +16544,6 @@
           <t>飞星</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>skill_name_middle11010</t>
@@ -14782,7 +16571,6 @@
           <t>震星</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>skill_name_middle11020</t>
@@ -14810,7 +16598,6 @@
           <t>裂星</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>skill_name_middle11030</t>
@@ -14838,7 +16625,6 @@
           <t>碎星</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>skill_name_middle11040</t>
@@ -14866,7 +16652,6 @@
           <t>震波</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>skill_name_middle11110</t>
@@ -14894,7 +16679,6 @@
           <t>动波</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>skill_name_middle11120</t>
@@ -14922,7 +16706,6 @@
           <t>烈波</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>skill_name_middle11130</t>
@@ -14950,7 +16733,6 @@
           <t>怒涛</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>skill_name_middle11140</t>
@@ -14978,7 +16760,6 @@
           <t>惊涛</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>skill_name_middle11150</t>
@@ -15006,7 +16787,6 @@
           <t>恨涛</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>skill_name_middle11160</t>
@@ -15034,7 +16814,6 @@
           <t>巨浪</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>skill_name_middle11170</t>
@@ -15062,7 +16841,6 @@
           <t>狂澜</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>skill_name_middle11180</t>
@@ -15090,7 +16868,6 @@
           <t>覆海</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>skill_name_middle11190</t>
@@ -15118,7 +16895,6 @@
           <t>火狱</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>skill_name_middle11210</t>
@@ -15146,7 +16922,6 @@
           <t>血狱</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>skill_name_middle11220</t>
@@ -15174,7 +16949,6 @@
           <t>冥狱</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>skill_name_middle11230</t>
@@ -15202,7 +16976,6 @@
           <t>荒狱</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>skill_name_middle11240</t>
@@ -15230,7 +17003,6 @@
           <t>鬼狱</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>skill_name_middle11250</t>
@@ -15258,7 +17030,6 @@
           <t>幽狱</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>skill_name_middle11260</t>
@@ -15286,7 +17057,6 @@
           <t>流云</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>skill_name_middle11310</t>
@@ -15314,7 +17084,6 @@
           <t>飞云</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>skill_name_middle11320</t>
@@ -15342,7 +17111,6 @@
           <t>疾云</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>skill_name_middle11330</t>
@@ -15370,7 +17138,6 @@
           <t>冲云</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>skill_name_middle11340</t>
@@ -15398,7 +17165,6 @@
           <t>火光</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>skill_name_middle11411</t>
@@ -15490,7 +17256,6 @@
           <t>冰气</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>skill_name_middle11421</t>
@@ -15582,7 +17347,6 @@
           <t>雷光</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>skill_name_middle11431</t>
@@ -15674,7 +17438,6 @@
           <t>翔风</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>skill_name_middle11441</t>
@@ -15766,7 +17529,6 @@
           <t>飞土</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>skill_name_middle11451</t>
@@ -15858,7 +17620,6 @@
           <t>灵木</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>skill_name_middle11461</t>
@@ -15950,7 +17711,6 @@
           <t>剑气1</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>skill_name_middle11511</t>
@@ -15978,7 +17738,6 @@
           <t>剑气2</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>skill_name_middle11512</t>
@@ -16006,7 +17765,6 @@
           <t>剑气3</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>skill_name_middle11513</t>
@@ -16034,7 +17792,6 @@
           <t>剑气4</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>skill_name_middle11514</t>
@@ -16062,7 +17819,6 @@
           <t>剑气5</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>skill_name_middle11515</t>
@@ -16090,7 +17846,6 @@
           <t>剑气6</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>skill_name_middle11516</t>
@@ -16118,7 +17873,6 @@
           <t>剑心1</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>skill_name_middle11611</t>
@@ -16146,7 +17900,6 @@
           <t>剑心2</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>skill_name_middle11612</t>
@@ -16174,7 +17927,6 @@
           <t>剑心3</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>skill_name_middle11613</t>
@@ -16202,7 +17954,6 @@
           <t>剑心4</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>skill_name_middle11614</t>
@@ -16230,7 +17981,6 @@
           <t>剑心5</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>skill_name_middle11615</t>
@@ -16258,7 +18008,6 @@
           <t>剑心6</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>skill_name_middle11616</t>
@@ -16286,7 +18035,6 @@
           <t>御气剑</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>skill_name_middle11711</t>
@@ -16314,7 +18062,6 @@
           <t>逸心剑</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>skill_name_middle11721</t>
@@ -16918,7 +18665,6 @@
           <t>降龙</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>skill_name_middle20011</t>
@@ -16946,7 +18692,6 @@
           <t>伏虎</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>skill_name_middle20021</t>
@@ -16974,7 +18719,6 @@
           <t>飞凤</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>skill_name_middle20031</t>
@@ -17002,7 +18746,6 @@
           <t>六合</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>skill_name_middle20041</t>
@@ -17030,7 +18773,6 @@
           <t>斩妖</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>skill_name_middle20051</t>
@@ -17058,7 +18800,6 @@
           <t>大荒</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>skill_name_middle20061</t>
@@ -17086,7 +18827,6 @@
           <t>万化</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>skill_name_middle20071</t>
@@ -17114,7 +18854,6 @@
           <t>独孤</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>skill_name_middle20081</t>
@@ -17142,7 +18881,6 @@
           <t>如来</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>skill_name_middle20091</t>
@@ -17170,7 +18908,6 @@
           <t>三清</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>skill_name_middle20101</t>
@@ -17198,7 +18935,6 @@
           <t>三阳</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>skill_name_middle20111</t>
@@ -17226,7 +18962,6 @@
           <t>六阳</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>skill_name_middle20121</t>
@@ -17254,7 +18989,6 @@
           <t>无相</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>skill_name_middle20131</t>
@@ -17282,7 +19016,6 @@
           <t>地煞</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>skill_name_middle20141</t>
@@ -17310,7 +19043,6 @@
           <t>天罡</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>skill_name_middle20151</t>
@@ -17338,7 +19070,6 @@
           <t>两仪</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>skill_name_middle20161</t>
@@ -17366,7 +19097,6 @@
           <t>四象</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>skill_name_middle20171</t>
@@ -17394,7 +19124,6 @@
           <t>八卦</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>skill_name_middle20181</t>
@@ -17422,7 +19151,6 @@
           <t>一气</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>skill_name_middle20191</t>
@@ -17450,7 +19178,6 @@
           <t>鬼谷</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>skill_name_middle20201</t>
@@ -17478,7 +19205,6 @@
           <t>御气</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>skill_name_middle20211</t>
@@ -17506,7 +19232,6 @@
           <t>御气</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>skill_name_middle20212</t>
@@ -17534,7 +19259,6 @@
           <t>化心</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>skill_name_middle20221</t>
@@ -17562,7 +19286,6 @@
           <t>灵影</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>skill_name_middle20231</t>
@@ -17590,7 +19313,6 @@
           <t>散雨</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>skill_name_middle20241</t>
@@ -17618,7 +19340,6 @@
           <t>落虹剑</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>skill_name_middle20251</t>
@@ -17646,7 +19367,6 @@
           <t>破空剑</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>skill_name_middle20261</t>
@@ -18922,7 +20642,6 @@
           <t>九阴</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>skill_name_middle30011</t>
@@ -18950,7 +20669,6 @@
           <t>九阳</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>skill_name_middle30021</t>
@@ -18978,7 +20696,6 @@
           <t>囚天</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>skill_name_middle30031</t>
@@ -34626,15 +36343,14 @@
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Como fica no jogo</t>
